--- a/research/traditional_assets/database/data/hungary/hungary_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_real_estate_general_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08201731116012673</v>
+        <v>0.08198444558008261</v>
       </c>
       <c r="C2">
-        <v>128.6145712639134</v>
+        <v>127.4673370246009</v>
       </c>
       <c r="D2">
-        <v>115.2145712639134</v>
+        <v>115.2633370246009</v>
       </c>
       <c r="E2">
-        <v>-38.1</v>
+        <v>-36.904</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.196</v>
       </c>
       <c r="G2">
         <v>13.4</v>
@@ -1451,28 +1451,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06015879999999999</v>
       </c>
       <c r="N2">
-        <v>6.033673469387756</v>
+        <v>5.973514669387756</v>
       </c>
       <c r="O2">
-        <v>0.543030612244898</v>
+        <v>0.537616320244898</v>
       </c>
       <c r="P2">
-        <v>5.490642857142857</v>
+        <v>5.435898349142858</v>
       </c>
       <c r="Q2">
-        <v>9.140642857142858</v>
+        <v>9.085898349142857</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08201731116012673</v>
+        <v>0.0823502177576592</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5318502034597871</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>100.295775005282</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08198444558008261</v>
+        <v>0.08195158000003851</v>
       </c>
       <c r="C3">
-        <v>127.4673370246009</v>
+        <v>126.3201440839951</v>
       </c>
       <c r="D3">
-        <v>115.2633370246009</v>
+        <v>115.3121440839951</v>
       </c>
       <c r="E3">
-        <v>-36.904</v>
+        <v>-35.708</v>
       </c>
       <c r="F3">
-        <v>1.196</v>
+        <v>2.392</v>
       </c>
       <c r="G3">
         <v>13.4</v>
@@ -1533,28 +1533,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M3">
-        <v>0.06015879999999999</v>
+        <v>0.1203176</v>
       </c>
       <c r="N3">
-        <v>5.973514669387756</v>
+        <v>5.913355869387756</v>
       </c>
       <c r="O3">
-        <v>0.537616320244898</v>
+        <v>0.532202028244898</v>
       </c>
       <c r="P3">
-        <v>5.435898349142858</v>
+        <v>5.381153841142858</v>
       </c>
       <c r="Q3">
-        <v>9.085898349142857</v>
+        <v>9.031153841142858</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0823502177576592</v>
+        <v>0.08268991836738622</v>
       </c>
       <c r="T3">
-        <v>0.5318502034597871</v>
+        <v>0.5367932612439194</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>100.295775005282</v>
+        <v>50.14788750264098</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08195158000003851</v>
+        <v>0.08191871441999438</v>
       </c>
       <c r="C4">
-        <v>126.3201440839951</v>
+        <v>125.1729924945809</v>
       </c>
       <c r="D4">
-        <v>115.3121440839951</v>
+        <v>115.3609924945809</v>
       </c>
       <c r="E4">
-        <v>-35.708</v>
+        <v>-34.512</v>
       </c>
       <c r="F4">
-        <v>2.392</v>
+        <v>3.588</v>
       </c>
       <c r="G4">
         <v>13.4</v>
@@ -1615,28 +1615,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M4">
-        <v>0.1203176</v>
+        <v>0.1804764</v>
       </c>
       <c r="N4">
-        <v>5.913355869387756</v>
+        <v>5.853197069387756</v>
       </c>
       <c r="O4">
-        <v>0.532202028244898</v>
+        <v>0.5267877362448981</v>
       </c>
       <c r="P4">
-        <v>5.381153841142858</v>
+        <v>5.326409333142857</v>
       </c>
       <c r="Q4">
-        <v>9.031153841142858</v>
+        <v>8.976409333142858</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08268991836738622</v>
+        <v>0.08303662311339627</v>
       </c>
       <c r="T4">
-        <v>0.5367932612439194</v>
+        <v>0.5418382377452503</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.14788750264098</v>
+        <v>33.43192500176065</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08191871441999438</v>
+        <v>0.08188584883995026</v>
       </c>
       <c r="C5">
-        <v>125.1729924945809</v>
+        <v>124.0258823089319</v>
       </c>
       <c r="D5">
-        <v>115.3609924945809</v>
+        <v>115.4098823089319</v>
       </c>
       <c r="E5">
-        <v>-34.512</v>
+        <v>-33.316</v>
       </c>
       <c r="F5">
-        <v>3.588</v>
+        <v>4.784</v>
       </c>
       <c r="G5">
         <v>13.4</v>
@@ -1697,28 +1697,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M5">
-        <v>0.1804764</v>
+        <v>0.2406352</v>
       </c>
       <c r="N5">
-        <v>5.853197069387756</v>
+        <v>5.793038269387756</v>
       </c>
       <c r="O5">
-        <v>0.5267877362448981</v>
+        <v>0.521373444244898</v>
       </c>
       <c r="P5">
-        <v>5.326409333142857</v>
+        <v>5.271664825142858</v>
       </c>
       <c r="Q5">
-        <v>8.976409333142858</v>
+        <v>8.921664825142857</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08303662311339627</v>
+        <v>0.08339055087494819</v>
       </c>
       <c r="T5">
-        <v>0.5418382377452503</v>
+        <v>0.5469883179236922</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.43192500176065</v>
+        <v>25.07394375132049</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08188584883995026</v>
+        <v>0.08185298325990616</v>
       </c>
       <c r="C6">
-        <v>124.0258823089319</v>
+        <v>122.8788135797109</v>
       </c>
       <c r="D6">
-        <v>115.4098823089319</v>
+        <v>115.4588135797109</v>
       </c>
       <c r="E6">
-        <v>-33.316</v>
+        <v>-32.12</v>
       </c>
       <c r="F6">
-        <v>4.784</v>
+        <v>5.98</v>
       </c>
       <c r="G6">
         <v>13.4</v>
@@ -1779,28 +1779,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M6">
-        <v>0.2406352</v>
+        <v>0.300794</v>
       </c>
       <c r="N6">
-        <v>5.793038269387756</v>
+        <v>5.732879469387756</v>
       </c>
       <c r="O6">
-        <v>0.521373444244898</v>
+        <v>0.515959152244898</v>
       </c>
       <c r="P6">
-        <v>5.271664825142858</v>
+        <v>5.216920317142858</v>
       </c>
       <c r="Q6">
-        <v>8.921664825142857</v>
+        <v>8.866920317142858</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08339055087494819</v>
+        <v>0.08375192974726964</v>
       </c>
       <c r="T6">
-        <v>0.5469883179236922</v>
+        <v>0.5522468208427329</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.07394375132049</v>
+        <v>20.05915500105639</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08185298325990616</v>
+        <v>0.08182011767986205</v>
       </c>
       <c r="C7">
-        <v>122.8788135797109</v>
+        <v>121.7317863596703</v>
       </c>
       <c r="D7">
-        <v>115.4588135797109</v>
+        <v>115.5077863596703</v>
       </c>
       <c r="E7">
-        <v>-32.12</v>
+        <v>-30.924</v>
       </c>
       <c r="F7">
-        <v>5.98</v>
+        <v>7.176</v>
       </c>
       <c r="G7">
         <v>13.4</v>
@@ -1861,28 +1861,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M7">
-        <v>0.300794</v>
+        <v>0.3609528</v>
       </c>
       <c r="N7">
-        <v>5.732879469387756</v>
+        <v>5.672720669387756</v>
       </c>
       <c r="O7">
-        <v>0.515959152244898</v>
+        <v>0.510544860244898</v>
       </c>
       <c r="P7">
-        <v>5.216920317142858</v>
+        <v>5.162175809142858</v>
       </c>
       <c r="Q7">
-        <v>8.866920317142858</v>
+        <v>8.812175809142857</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08375192974726964</v>
+        <v>0.08412099753176813</v>
       </c>
       <c r="T7">
-        <v>0.5522468208427329</v>
+        <v>0.5576172068026044</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.05915500105639</v>
+        <v>16.71596250088033</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08182011767986205</v>
+        <v>0.08178725209981792</v>
       </c>
       <c r="C8">
-        <v>121.7317863596703</v>
+        <v>120.5848007016518</v>
       </c>
       <c r="D8">
-        <v>115.5077863596703</v>
+        <v>115.5568007016518</v>
       </c>
       <c r="E8">
-        <v>-30.924</v>
+        <v>-29.728</v>
       </c>
       <c r="F8">
-        <v>7.175999999999999</v>
+        <v>8.371999999999998</v>
       </c>
       <c r="G8">
         <v>13.4</v>
@@ -1943,28 +1943,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M8">
-        <v>0.3609528</v>
+        <v>0.4211115999999999</v>
       </c>
       <c r="N8">
-        <v>5.672720669387756</v>
+        <v>5.612561869387756</v>
       </c>
       <c r="O8">
-        <v>0.510544860244898</v>
+        <v>0.505130568244898</v>
       </c>
       <c r="P8">
-        <v>5.162175809142858</v>
+        <v>5.107431301142858</v>
       </c>
       <c r="Q8">
-        <v>8.812175809142857</v>
+        <v>8.757431301142859</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08412099753176813</v>
+        <v>0.08449800225786873</v>
       </c>
       <c r="T8">
-        <v>0.5576172068026044</v>
+        <v>0.5631030849336558</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.71596250088033</v>
+        <v>14.32796785789743</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08178725209981792</v>
+        <v>0.08186358651977382</v>
       </c>
       <c r="C9">
-        <v>120.5848007016518</v>
+        <v>119.2750225922141</v>
       </c>
       <c r="D9">
-        <v>115.5568007016518</v>
+        <v>115.4430225922141</v>
       </c>
       <c r="E9">
-        <v>-29.728</v>
+        <v>-28.532</v>
       </c>
       <c r="F9">
-        <v>8.372</v>
+        <v>9.568</v>
       </c>
       <c r="G9">
         <v>13.4</v>
@@ -2025,45 +2025,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M9">
-        <v>0.4211116</v>
+        <v>0.4956224</v>
       </c>
       <c r="N9">
-        <v>5.612561869387756</v>
+        <v>5.538051069387755</v>
       </c>
       <c r="O9">
-        <v>0.505130568244898</v>
+        <v>0.498424596244898</v>
       </c>
       <c r="P9">
-        <v>5.107431301142858</v>
+        <v>5.039626473142857</v>
       </c>
       <c r="Q9">
-        <v>8.757431301142859</v>
+        <v>8.689626473142857</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08449800225786874</v>
+        <v>0.08488320273888458</v>
       </c>
       <c r="T9">
-        <v>0.5631030849336559</v>
+        <v>0.5687082212849476</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.09</v>
       </c>
       <c r="W9">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.32796785789742</v>
+        <v>12.17393214953109</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08186358651977382</v>
+        <v>0.08184437093972971</v>
       </c>
       <c r="C10">
-        <v>119.2750225922141</v>
+        <v>118.1076427244944</v>
       </c>
       <c r="D10">
-        <v>115.4430225922141</v>
+        <v>115.4716427244944</v>
       </c>
       <c r="E10">
-        <v>-28.532</v>
+        <v>-27.336</v>
       </c>
       <c r="F10">
-        <v>9.568</v>
+        <v>10.764</v>
       </c>
       <c r="G10">
         <v>13.4</v>
@@ -2107,28 +2107,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M10">
-        <v>0.4956224</v>
+        <v>0.5575751999999999</v>
       </c>
       <c r="N10">
-        <v>5.538051069387755</v>
+        <v>5.476098269387756</v>
       </c>
       <c r="O10">
-        <v>0.498424596244898</v>
+        <v>0.492848844244898</v>
       </c>
       <c r="P10">
-        <v>5.039626473142857</v>
+        <v>4.983249425142858</v>
       </c>
       <c r="Q10">
-        <v>8.689626473142857</v>
+        <v>8.633249425142857</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08488320273888458</v>
+        <v>0.08527686916453814</v>
       </c>
       <c r="T10">
-        <v>0.5687082212849476</v>
+        <v>0.5744365474461578</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.17393214953109</v>
+        <v>10.82127302180541</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08184437093972971</v>
+        <v>0.08197985535968558</v>
       </c>
       <c r="C11">
-        <v>118.1076427244944</v>
+        <v>116.7101512531381</v>
       </c>
       <c r="D11">
-        <v>115.4716427244944</v>
+        <v>115.2701512531381</v>
       </c>
       <c r="E11">
-        <v>-27.336</v>
+        <v>-26.14</v>
       </c>
       <c r="F11">
-        <v>10.764</v>
+        <v>11.96</v>
       </c>
       <c r="G11">
         <v>13.4</v>
@@ -2189,45 +2189,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M11">
-        <v>0.5575751999999999</v>
+        <v>0.63986</v>
       </c>
       <c r="N11">
-        <v>5.476098269387756</v>
+        <v>5.393813469387756</v>
       </c>
       <c r="O11">
-        <v>0.492848844244898</v>
+        <v>0.485443212244898</v>
       </c>
       <c r="P11">
-        <v>4.983249425142858</v>
+        <v>4.908370257142858</v>
       </c>
       <c r="Q11">
-        <v>8.633249425142857</v>
+        <v>8.558370257142858</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08527686916453814</v>
+        <v>0.08567928373298397</v>
       </c>
       <c r="T11">
-        <v>0.5744365474461578</v>
+        <v>0.5802921697442837</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.09</v>
       </c>
       <c r="W11">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.82127302180541</v>
+        <v>9.42967753787978</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08197985535968558</v>
+        <v>0.08197610977964145</v>
       </c>
       <c r="C12">
-        <v>116.7101512531381</v>
+        <v>115.5197122015249</v>
       </c>
       <c r="D12">
-        <v>115.2701512531381</v>
+        <v>115.2757122015249</v>
       </c>
       <c r="E12">
-        <v>-26.14</v>
+        <v>-24.944</v>
       </c>
       <c r="F12">
-        <v>11.96</v>
+        <v>13.156</v>
       </c>
       <c r="G12">
         <v>13.4</v>
@@ -2271,28 +2271,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M12">
-        <v>0.63986</v>
+        <v>0.703846</v>
       </c>
       <c r="N12">
-        <v>5.393813469387756</v>
+        <v>5.329827469387755</v>
       </c>
       <c r="O12">
-        <v>0.485443212244898</v>
+        <v>0.479684472244898</v>
       </c>
       <c r="P12">
-        <v>4.908370257142858</v>
+        <v>4.850142997142857</v>
       </c>
       <c r="Q12">
-        <v>8.558370257142858</v>
+        <v>8.500142997142857</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08567928373298397</v>
+        <v>0.08609074132543984</v>
       </c>
       <c r="T12">
-        <v>0.5802921697442837</v>
+        <v>0.586279379060345</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.42967753787978</v>
+        <v>8.572434125345254</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08197610977964145</v>
+        <v>0.08197236419959736</v>
       </c>
       <c r="C13">
-        <v>115.5197122015249</v>
+        <v>114.3292736864884</v>
       </c>
       <c r="D13">
-        <v>115.2757122015249</v>
+        <v>115.2812736864884</v>
       </c>
       <c r="E13">
-        <v>-24.944</v>
+        <v>-23.748</v>
       </c>
       <c r="F13">
-        <v>13.156</v>
+        <v>14.352</v>
       </c>
       <c r="G13">
         <v>13.4</v>
@@ -2353,28 +2353,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M13">
-        <v>0.703846</v>
+        <v>0.767832</v>
       </c>
       <c r="N13">
-        <v>5.329827469387755</v>
+        <v>5.265841469387755</v>
       </c>
       <c r="O13">
-        <v>0.479684472244898</v>
+        <v>0.473925732244898</v>
       </c>
       <c r="P13">
-        <v>4.850142997142857</v>
+        <v>4.791915737142857</v>
       </c>
       <c r="Q13">
-        <v>8.500142997142857</v>
+        <v>8.441915737142857</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08609074132543984</v>
+        <v>0.08651155022681517</v>
       </c>
       <c r="T13">
-        <v>0.586279379060345</v>
+        <v>0.5924026613154079</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.572434125345254</v>
+        <v>7.858064614899816</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08197236419959736</v>
+        <v>0.08206325861955323</v>
       </c>
       <c r="C14">
-        <v>114.3292736864884</v>
+        <v>112.9984638138207</v>
       </c>
       <c r="D14">
-        <v>115.2812736864884</v>
+        <v>115.1464638138207</v>
       </c>
       <c r="E14">
-        <v>-23.748</v>
+        <v>-22.552</v>
       </c>
       <c r="F14">
-        <v>14.352</v>
+        <v>15.548</v>
       </c>
       <c r="G14">
         <v>13.4</v>
@@ -2435,45 +2435,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M14">
-        <v>0.767832</v>
+        <v>0.8442564</v>
       </c>
       <c r="N14">
-        <v>5.265841469387755</v>
+        <v>5.189417069387756</v>
       </c>
       <c r="O14">
-        <v>0.473925732244898</v>
+        <v>0.467047536244898</v>
       </c>
       <c r="P14">
-        <v>4.791915737142857</v>
+        <v>4.722369533142857</v>
       </c>
       <c r="Q14">
-        <v>8.441915737142857</v>
+        <v>8.372369533142857</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08651155022681517</v>
+        <v>0.0869420328960382</v>
       </c>
       <c r="T14">
-        <v>0.5924026613154079</v>
+        <v>0.5986667086797824</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.09</v>
       </c>
       <c r="W14">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.858064614899816</v>
+        <v>7.146731098973908</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08206325861955323</v>
+        <v>0.08206679303950913</v>
       </c>
       <c r="C15">
-        <v>112.9984638138207</v>
+        <v>111.7972281142564</v>
       </c>
       <c r="D15">
-        <v>115.1464638138207</v>
+        <v>115.1412281142564</v>
       </c>
       <c r="E15">
-        <v>-22.552</v>
+        <v>-21.356</v>
       </c>
       <c r="F15">
-        <v>15.548</v>
+        <v>16.744</v>
       </c>
       <c r="G15">
         <v>13.4</v>
@@ -2517,28 +2517,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M15">
-        <v>0.8442564</v>
+        <v>0.9091992</v>
       </c>
       <c r="N15">
-        <v>5.189417069387756</v>
+        <v>5.124474269387756</v>
       </c>
       <c r="O15">
-        <v>0.467047536244898</v>
+        <v>0.461202684244898</v>
       </c>
       <c r="P15">
-        <v>4.722369533142857</v>
+        <v>4.663271585142858</v>
       </c>
       <c r="Q15">
-        <v>8.372369533142857</v>
+        <v>8.313271585142857</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0869420328960382</v>
+        <v>0.0873825267901269</v>
       </c>
       <c r="T15">
-        <v>0.5986667086797824</v>
+        <v>0.6050764315642587</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.146731098973908</v>
+        <v>6.636250306190058</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08206679303950913</v>
+        <v>0.08207032745946501</v>
       </c>
       <c r="C16">
-        <v>111.7972281142564</v>
+        <v>110.595992890804</v>
       </c>
       <c r="D16">
-        <v>115.1412281142564</v>
+        <v>115.135992890804</v>
       </c>
       <c r="E16">
-        <v>-21.356</v>
+        <v>-20.16</v>
       </c>
       <c r="F16">
-        <v>16.744</v>
+        <v>17.94</v>
       </c>
       <c r="G16">
         <v>13.4</v>
@@ -2599,28 +2599,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M16">
-        <v>0.9091992</v>
+        <v>0.9741420000000001</v>
       </c>
       <c r="N16">
-        <v>5.124474269387756</v>
+        <v>5.059531469387755</v>
       </c>
       <c r="O16">
-        <v>0.461202684244898</v>
+        <v>0.455357832244898</v>
       </c>
       <c r="P16">
-        <v>4.663271585142858</v>
+        <v>4.604173637142857</v>
       </c>
       <c r="Q16">
-        <v>8.313271585142857</v>
+        <v>8.254173637142857</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0873825267901269</v>
+        <v>0.08783338524642942</v>
       </c>
       <c r="T16">
-        <v>0.6050764315642587</v>
+        <v>0.6116369714577815</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.636250306190058</v>
+        <v>6.19383361911072</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08207032745946501</v>
+        <v>0.0822194618794209</v>
       </c>
       <c r="C17">
-        <v>110.595992890804</v>
+        <v>109.1795262855273</v>
       </c>
       <c r="D17">
-        <v>115.135992890804</v>
+        <v>114.9155262855273</v>
       </c>
       <c r="E17">
-        <v>-20.16</v>
+        <v>-18.964</v>
       </c>
       <c r="F17">
-        <v>17.94</v>
+        <v>19.136</v>
       </c>
       <c r="G17">
         <v>13.4</v>
@@ -2681,45 +2681,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M17">
-        <v>0.9741419999999998</v>
+        <v>1.0582208</v>
       </c>
       <c r="N17">
-        <v>5.059531469387756</v>
+        <v>4.975452669387756</v>
       </c>
       <c r="O17">
-        <v>0.455357832244898</v>
+        <v>0.447790740244898</v>
       </c>
       <c r="P17">
-        <v>4.604173637142858</v>
+        <v>4.527661929142858</v>
       </c>
       <c r="Q17">
-        <v>8.254173637142857</v>
+        <v>8.177661929142857</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08783338524642942</v>
+        <v>0.08829497842788203</v>
       </c>
       <c r="T17">
-        <v>0.6116369714577815</v>
+        <v>0.6183537146821025</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.09</v>
       </c>
       <c r="W17">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.193833619110722</v>
+        <v>5.701715057375319</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0822194618794209</v>
+        <v>0.08223209629937678</v>
       </c>
       <c r="C18">
-        <v>109.1795262855273</v>
+        <v>107.9648875095976</v>
       </c>
       <c r="D18">
-        <v>114.9155262855273</v>
+        <v>114.8968875095976</v>
       </c>
       <c r="E18">
-        <v>-18.964</v>
+        <v>-17.768</v>
       </c>
       <c r="F18">
-        <v>19.136</v>
+        <v>20.332</v>
       </c>
       <c r="G18">
         <v>13.4</v>
@@ -2763,28 +2763,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M18">
-        <v>1.0582208</v>
+        <v>1.1243596</v>
       </c>
       <c r="N18">
-        <v>4.975452669387756</v>
+        <v>4.909313869387756</v>
       </c>
       <c r="O18">
-        <v>0.447790740244898</v>
+        <v>0.441838248244898</v>
       </c>
       <c r="P18">
-        <v>4.527661929142858</v>
+        <v>4.467475621142857</v>
       </c>
       <c r="Q18">
-        <v>8.177661929142857</v>
+        <v>8.117475621142857</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08829497842788203</v>
+        <v>0.08876769433659853</v>
       </c>
       <c r="T18">
-        <v>0.6183537146821025</v>
+        <v>0.6252323071407444</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.701715057375319</v>
+        <v>5.3663200540003</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08223209629937678</v>
+        <v>0.08224473071933266</v>
       </c>
       <c r="C19">
-        <v>107.9648875095976</v>
+        <v>106.7502547789368</v>
       </c>
       <c r="D19">
-        <v>114.8968875095976</v>
+        <v>114.8782547789369</v>
       </c>
       <c r="E19">
-        <v>-17.768</v>
+        <v>-16.572</v>
       </c>
       <c r="F19">
-        <v>20.332</v>
+        <v>21.528</v>
       </c>
       <c r="G19">
         <v>13.4</v>
@@ -2845,28 +2845,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M19">
-        <v>1.1243596</v>
+        <v>1.1904984</v>
       </c>
       <c r="N19">
-        <v>4.909313869387756</v>
+        <v>4.843175069387756</v>
       </c>
       <c r="O19">
-        <v>0.441838248244898</v>
+        <v>0.435885756244898</v>
       </c>
       <c r="P19">
-        <v>4.467475621142857</v>
+        <v>4.407289313142858</v>
       </c>
       <c r="Q19">
-        <v>8.117475621142857</v>
+        <v>8.057289313142858</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08876769433659853</v>
+        <v>0.08925193990162519</v>
       </c>
       <c r="T19">
-        <v>0.6252323071407444</v>
+        <v>0.6322786701471581</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.3663200540003</v>
+        <v>5.068191162111394</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08224473071933266</v>
+        <v>0.08225736513928855</v>
       </c>
       <c r="C20">
-        <v>106.7502547789369</v>
+        <v>105.5356280906044</v>
       </c>
       <c r="D20">
-        <v>114.8782547789369</v>
+        <v>114.8596280906044</v>
       </c>
       <c r="E20">
-        <v>-16.572</v>
+        <v>-15.376</v>
       </c>
       <c r="F20">
-        <v>21.528</v>
+        <v>22.724</v>
       </c>
       <c r="G20">
         <v>13.4</v>
@@ -2927,28 +2927,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M20">
-        <v>1.1904984</v>
+        <v>1.2566372</v>
       </c>
       <c r="N20">
-        <v>4.843175069387756</v>
+        <v>4.777036269387755</v>
       </c>
       <c r="O20">
-        <v>0.435885756244898</v>
+        <v>0.429933264244898</v>
       </c>
       <c r="P20">
-        <v>4.407289313142858</v>
+        <v>4.347103005142857</v>
       </c>
       <c r="Q20">
-        <v>8.057289313142858</v>
+        <v>7.997103005142858</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08925193990162519</v>
+        <v>0.08974814214726981</v>
       </c>
       <c r="T20">
-        <v>0.6322786701471581</v>
+        <v>0.6394990174253351</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.068191162111394</v>
+        <v>4.801444258842373</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08225736513928855</v>
+        <v>0.08226999955924445</v>
       </c>
       <c r="C21">
-        <v>105.5356280906044</v>
+        <v>104.3210074416616</v>
       </c>
       <c r="D21">
-        <v>114.8596280906044</v>
+        <v>114.8410074416616</v>
       </c>
       <c r="E21">
-        <v>-15.376</v>
+        <v>-14.18</v>
       </c>
       <c r="F21">
-        <v>22.724</v>
+        <v>23.92</v>
       </c>
       <c r="G21">
         <v>13.4</v>
@@ -3009,28 +3009,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M21">
-        <v>1.2566372</v>
+        <v>1.322776</v>
       </c>
       <c r="N21">
-        <v>4.777036269387755</v>
+        <v>4.710897469387755</v>
       </c>
       <c r="O21">
-        <v>0.429933264244898</v>
+        <v>0.423980772244898</v>
       </c>
       <c r="P21">
-        <v>4.347103005142857</v>
+        <v>4.286916697142858</v>
       </c>
       <c r="Q21">
-        <v>7.997103005142858</v>
+        <v>7.936916697142857</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08974814214726981</v>
+        <v>0.09025674944905555</v>
       </c>
       <c r="T21">
-        <v>0.6394990174253351</v>
+        <v>0.6468998733854666</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.801444258842373</v>
+        <v>4.561372045900255</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08226999955924445</v>
+        <v>0.08276038397920032</v>
       </c>
       <c r="C22">
-        <v>104.3210074416616</v>
+        <v>102.4069129252948</v>
       </c>
       <c r="D22">
-        <v>114.8410074416616</v>
+        <v>114.1229129252948</v>
       </c>
       <c r="E22">
-        <v>-14.18</v>
+        <v>-12.984</v>
       </c>
       <c r="F22">
-        <v>23.92</v>
+        <v>25.116</v>
       </c>
       <c r="G22">
         <v>13.4</v>
@@ -3091,45 +3091,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M22">
-        <v>1.322776</v>
+        <v>1.4517048</v>
       </c>
       <c r="N22">
-        <v>4.710897469387755</v>
+        <v>4.581968669387756</v>
       </c>
       <c r="O22">
-        <v>0.423980772244898</v>
+        <v>0.412377180244898</v>
       </c>
       <c r="P22">
-        <v>4.286916697142858</v>
+        <v>4.169591489142857</v>
       </c>
       <c r="Q22">
-        <v>7.936916697142857</v>
+        <v>7.819591489142857</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09025674944905555</v>
+        <v>0.0907782328850637</v>
       </c>
       <c r="T22">
-        <v>0.6468998733854666</v>
+        <v>0.6544880927876267</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.09</v>
       </c>
       <c r="W22">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.561372045900255</v>
+        <v>4.156267492804154</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08276038397920032</v>
+        <v>0.08349646839915623</v>
       </c>
       <c r="C23">
-        <v>102.4069129252948</v>
+        <v>100.1497276968448</v>
       </c>
       <c r="D23">
-        <v>114.1229129252948</v>
+        <v>113.0617276968448</v>
       </c>
       <c r="E23">
-        <v>-12.98400000000001</v>
+        <v>-11.788</v>
       </c>
       <c r="F23">
-        <v>25.116</v>
+        <v>26.312</v>
       </c>
       <c r="G23">
         <v>13.4</v>
@@ -3173,45 +3173,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M23">
-        <v>1.4517048</v>
+        <v>1.6129256</v>
       </c>
       <c r="N23">
-        <v>4.581968669387756</v>
+        <v>4.420747869387756</v>
       </c>
       <c r="O23">
-        <v>0.412377180244898</v>
+        <v>0.397867308244898</v>
       </c>
       <c r="P23">
-        <v>4.169591489142857</v>
+        <v>4.022880561142858</v>
       </c>
       <c r="Q23">
-        <v>7.819591489142857</v>
+        <v>7.672880561142858</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0907782328850637</v>
+        <v>0.09131308769122591</v>
       </c>
       <c r="T23">
-        <v>0.6544880927876267</v>
+        <v>0.6622708819180473</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.09</v>
       </c>
       <c r="W23">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.156267492804155</v>
+        <v>3.740825658286877</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08349646839915623</v>
+        <v>0.0835637028191121</v>
       </c>
       <c r="C24">
-        <v>100.1497276968448</v>
+        <v>98.85778116200294</v>
       </c>
       <c r="D24">
-        <v>113.0617276968448</v>
+        <v>112.9657811620029</v>
       </c>
       <c r="E24">
-        <v>-11.788</v>
+        <v>-10.592</v>
       </c>
       <c r="F24">
-        <v>26.312</v>
+        <v>27.508</v>
       </c>
       <c r="G24">
         <v>13.4</v>
@@ -3255,28 +3255,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M24">
-        <v>1.6129256</v>
+        <v>1.6862404</v>
       </c>
       <c r="N24">
-        <v>4.420747869387756</v>
+        <v>4.347433069387756</v>
       </c>
       <c r="O24">
-        <v>0.397867308244898</v>
+        <v>0.391268976244898</v>
       </c>
       <c r="P24">
-        <v>4.022880561142858</v>
+        <v>3.956164093142858</v>
       </c>
       <c r="Q24">
-        <v>7.672880561142858</v>
+        <v>7.606164093142858</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09131308769122591</v>
+        <v>0.09186183483001571</v>
       </c>
       <c r="T24">
-        <v>0.6622708819180473</v>
+        <v>0.6702558214154918</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.740825658286877</v>
+        <v>3.578181064448317</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0835637028191121</v>
+        <v>0.08424245723906799</v>
       </c>
       <c r="C25">
-        <v>98.85778116200294</v>
+        <v>96.70221087719935</v>
       </c>
       <c r="D25">
-        <v>112.9657811620029</v>
+        <v>112.0062108771994</v>
       </c>
       <c r="E25">
-        <v>-10.592</v>
+        <v>-9.396000000000001</v>
       </c>
       <c r="F25">
-        <v>27.508</v>
+        <v>28.704</v>
       </c>
       <c r="G25">
         <v>13.4</v>
@@ -3337,45 +3337,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M25">
-        <v>1.6862404</v>
+        <v>1.8399264</v>
       </c>
       <c r="N25">
-        <v>4.347433069387756</v>
+        <v>4.193747069387755</v>
       </c>
       <c r="O25">
-        <v>0.391268976244898</v>
+        <v>0.3774372362448979</v>
       </c>
       <c r="P25">
-        <v>3.956164093142858</v>
+        <v>3.816309833142857</v>
       </c>
       <c r="Q25">
-        <v>7.606164093142858</v>
+        <v>7.466309833142857</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09186183483001571</v>
+        <v>0.09242502268298419</v>
       </c>
       <c r="T25">
-        <v>0.6702558214154918</v>
+        <v>0.6784508908997112</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.09</v>
       </c>
       <c r="W25">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.578181064448317</v>
+        <v>3.279301535859127</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08424245723906799</v>
+        <v>0.08433517165902388</v>
       </c>
       <c r="C26">
-        <v>96.70221087719936</v>
+        <v>95.37640242003297</v>
       </c>
       <c r="D26">
-        <v>112.0062108771994</v>
+        <v>111.876402420033</v>
       </c>
       <c r="E26">
-        <v>-9.396000000000004</v>
+        <v>-8.200000000000003</v>
       </c>
       <c r="F26">
-        <v>28.704</v>
+        <v>29.9</v>
       </c>
       <c r="G26">
         <v>13.4</v>
@@ -3419,28 +3419,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M26">
-        <v>1.8399264</v>
+        <v>1.91659</v>
       </c>
       <c r="N26">
-        <v>4.193747069387756</v>
+        <v>4.117083469387755</v>
       </c>
       <c r="O26">
-        <v>0.3774372362448981</v>
+        <v>0.3705375122448979</v>
       </c>
       <c r="P26">
-        <v>3.816309833142858</v>
+        <v>3.746545957142858</v>
       </c>
       <c r="Q26">
-        <v>7.466309833142859</v>
+        <v>7.396545957142857</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09242502268298419</v>
+        <v>0.0930032288786985</v>
       </c>
       <c r="T26">
-        <v>0.6784508908997111</v>
+        <v>0.6868644955701763</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.279301535859128</v>
+        <v>3.148129474424763</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08433517165902388</v>
+        <v>0.08442788607897975</v>
       </c>
       <c r="C27">
-        <v>95.37640242003297</v>
+        <v>94.05089449494633</v>
       </c>
       <c r="D27">
-        <v>111.876402420033</v>
+        <v>111.7468944949463</v>
       </c>
       <c r="E27">
-        <v>-8.200000000000003</v>
+        <v>-7.004000000000001</v>
       </c>
       <c r="F27">
-        <v>29.9</v>
+        <v>31.096</v>
       </c>
       <c r="G27">
         <v>13.4</v>
@@ -3501,28 +3501,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M27">
-        <v>1.91659</v>
+        <v>1.9932536</v>
       </c>
       <c r="N27">
-        <v>4.117083469387755</v>
+        <v>4.040419869387756</v>
       </c>
       <c r="O27">
-        <v>0.3705375122448979</v>
+        <v>0.363637788244898</v>
       </c>
       <c r="P27">
-        <v>3.746545957142858</v>
+        <v>3.676782081142858</v>
       </c>
       <c r="Q27">
-        <v>7.396545957142857</v>
+        <v>7.326782081142857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0930032288786985</v>
+        <v>0.09359706226889156</v>
       </c>
       <c r="T27">
-        <v>0.6868644955701763</v>
+        <v>0.695505494961465</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.148129474424763</v>
+        <v>3.027047571562272</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08442788607897975</v>
+        <v>0.08643706049893563</v>
       </c>
       <c r="C28">
-        <v>94.05089449494633</v>
+        <v>90.12023381244936</v>
       </c>
       <c r="D28">
-        <v>111.7468944949463</v>
+        <v>109.0122338124494</v>
       </c>
       <c r="E28">
-        <v>-7.004000000000001</v>
+        <v>-5.808</v>
       </c>
       <c r="F28">
-        <v>31.096</v>
+        <v>32.292</v>
       </c>
       <c r="G28">
         <v>13.4</v>
@@ -3583,45 +3583,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M28">
-        <v>1.9932536</v>
+        <v>2.3217948</v>
       </c>
       <c r="N28">
-        <v>4.040419869387756</v>
+        <v>3.711878669387755</v>
       </c>
       <c r="O28">
-        <v>0.363637788244898</v>
+        <v>0.334069080244898</v>
       </c>
       <c r="P28">
-        <v>3.676782081142858</v>
+        <v>3.377809589142858</v>
       </c>
       <c r="Q28">
-        <v>7.326782081142857</v>
+        <v>7.027809589142858</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09359706226889156</v>
+        <v>0.09420716506703512</v>
       </c>
       <c r="T28">
-        <v>0.695505494961465</v>
+        <v>0.7043832340621039</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.09</v>
       </c>
       <c r="W28">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.027047571562272</v>
+        <v>2.598710906488272</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08643706049893563</v>
+        <v>0.08660075491889155</v>
       </c>
       <c r="C29">
-        <v>90.12023381244936</v>
+        <v>88.70731639832341</v>
       </c>
       <c r="D29">
-        <v>109.0122338124494</v>
+        <v>108.7953163983234</v>
       </c>
       <c r="E29">
-        <v>-5.808</v>
+        <v>-4.612000000000002</v>
       </c>
       <c r="F29">
-        <v>32.292</v>
+        <v>33.488</v>
       </c>
       <c r="G29">
         <v>13.4</v>
@@ -3665,28 +3665,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M29">
-        <v>2.3217948</v>
+        <v>2.4077872</v>
       </c>
       <c r="N29">
-        <v>3.711878669387755</v>
+        <v>3.625886269387756</v>
       </c>
       <c r="O29">
-        <v>0.334069080244898</v>
+        <v>0.326329764244898</v>
       </c>
       <c r="P29">
-        <v>3.377809589142858</v>
+        <v>3.299556505142858</v>
       </c>
       <c r="Q29">
-        <v>7.027809589142858</v>
+        <v>6.949556505142858</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09420716506703512</v>
+        <v>0.09483421516512713</v>
       </c>
       <c r="T29">
-        <v>0.7043832340621039</v>
+        <v>0.7135075770266496</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.598710906488272</v>
+        <v>2.505899802685119</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08660075491889155</v>
+        <v>0.08779365933884742</v>
       </c>
       <c r="C30">
-        <v>88.70731639832341</v>
+        <v>85.95625059166329</v>
       </c>
       <c r="D30">
-        <v>108.7953163983234</v>
+        <v>107.2402505916633</v>
       </c>
       <c r="E30">
-        <v>-4.612000000000002</v>
+        <v>-3.415999999999997</v>
       </c>
       <c r="F30">
-        <v>33.488</v>
+        <v>34.684</v>
       </c>
       <c r="G30">
         <v>13.4</v>
@@ -3747,45 +3747,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M30">
-        <v>2.4077872</v>
+        <v>2.6290472</v>
       </c>
       <c r="N30">
-        <v>3.625886269387756</v>
+        <v>3.404626269387755</v>
       </c>
       <c r="O30">
-        <v>0.326329764244898</v>
+        <v>0.3064163642448979</v>
       </c>
       <c r="P30">
-        <v>3.299556505142858</v>
+        <v>3.098209905142857</v>
       </c>
       <c r="Q30">
-        <v>6.949556505142858</v>
+        <v>6.748209905142858</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09483421516512713</v>
+        <v>0.09547892864626396</v>
       </c>
       <c r="T30">
-        <v>0.7135075770266496</v>
+        <v>0.7228889437366753</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.09</v>
       </c>
       <c r="W30">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.505899802685119</v>
+        <v>2.295003858959913</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0877936593388474</v>
+        <v>0.0879928437588033</v>
       </c>
       <c r="C31">
-        <v>85.95625059166331</v>
+        <v>84.50491530503785</v>
       </c>
       <c r="D31">
-        <v>107.2402505916633</v>
+        <v>106.9849153050378</v>
       </c>
       <c r="E31">
-        <v>-3.416000000000004</v>
+        <v>-2.220000000000006</v>
       </c>
       <c r="F31">
-        <v>34.684</v>
+        <v>35.88</v>
       </c>
       <c r="G31">
         <v>13.4</v>
@@ -3829,28 +3829,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M31">
-        <v>2.6290472</v>
+        <v>2.719704</v>
       </c>
       <c r="N31">
-        <v>3.404626269387756</v>
+        <v>3.313969469387756</v>
       </c>
       <c r="O31">
-        <v>0.306416364244898</v>
+        <v>0.298257252244898</v>
       </c>
       <c r="P31">
-        <v>3.098209905142858</v>
+        <v>3.015712217142858</v>
       </c>
       <c r="Q31">
-        <v>6.748209905142858</v>
+        <v>6.665712217142858</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09547892864626395</v>
+        <v>0.09614206251257615</v>
       </c>
       <c r="T31">
-        <v>0.7228889437366752</v>
+        <v>0.732538349495559</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.295003858959913</v>
+        <v>2.218503730327916</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0879928437588033</v>
+        <v>0.08819202817875919</v>
       </c>
       <c r="C32">
-        <v>84.50491530503785</v>
+        <v>83.05479301907775</v>
       </c>
       <c r="D32">
-        <v>106.9849153050378</v>
+        <v>106.7307930190777</v>
       </c>
       <c r="E32">
-        <v>-2.220000000000006</v>
+        <v>-1.024000000000001</v>
       </c>
       <c r="F32">
-        <v>35.88</v>
+        <v>37.076</v>
       </c>
       <c r="G32">
         <v>13.4</v>
@@ -3911,28 +3911,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M32">
-        <v>2.719704</v>
+        <v>2.8103608</v>
       </c>
       <c r="N32">
-        <v>3.313969469387756</v>
+        <v>3.223312669387755</v>
       </c>
       <c r="O32">
-        <v>0.298257252244898</v>
+        <v>0.290098140244898</v>
       </c>
       <c r="P32">
-        <v>3.015712217142858</v>
+        <v>2.933214529142858</v>
       </c>
       <c r="Q32">
-        <v>6.665712217142858</v>
+        <v>6.583214529142857</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09614206251257615</v>
+        <v>0.09682441765037564</v>
       </c>
       <c r="T32">
-        <v>0.732538349495559</v>
+        <v>0.7424674481749899</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.218503730327916</v>
+        <v>2.146939093865726</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08819202817875919</v>
+        <v>0.08839121259871507</v>
       </c>
       <c r="C33">
-        <v>83.05479301907775</v>
+        <v>81.60587511050991</v>
       </c>
       <c r="D33">
-        <v>106.7307930190777</v>
+        <v>106.4778751105099</v>
       </c>
       <c r="E33">
-        <v>-1.024000000000001</v>
+        <v>0.171999999999997</v>
       </c>
       <c r="F33">
-        <v>37.076</v>
+        <v>38.272</v>
       </c>
       <c r="G33">
         <v>13.4</v>
@@ -3993,28 +3993,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M33">
-        <v>2.8103608</v>
+        <v>2.9010176</v>
       </c>
       <c r="N33">
-        <v>3.223312669387755</v>
+        <v>3.132655869387755</v>
       </c>
       <c r="O33">
-        <v>0.290098140244898</v>
+        <v>0.281939028244898</v>
       </c>
       <c r="P33">
-        <v>2.933214529142858</v>
+        <v>2.850716841142857</v>
       </c>
       <c r="Q33">
-        <v>6.583214529142857</v>
+        <v>6.500716841142857</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09682441765037564</v>
+        <v>0.09752684205693393</v>
       </c>
       <c r="T33">
-        <v>0.7424674481749899</v>
+        <v>0.7526885791685218</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.146939093865726</v>
+        <v>2.079847247182421</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08839121259871507</v>
+        <v>0.08859039701867095</v>
       </c>
       <c r="C34">
-        <v>81.60587511050991</v>
+        <v>80.15815303760566</v>
       </c>
       <c r="D34">
-        <v>106.4778751105099</v>
+        <v>106.2261530376057</v>
       </c>
       <c r="E34">
-        <v>0.171999999999997</v>
+        <v>1.368000000000002</v>
       </c>
       <c r="F34">
-        <v>38.272</v>
+        <v>39.468</v>
       </c>
       <c r="G34">
         <v>13.4</v>
@@ -4075,28 +4075,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M34">
-        <v>2.9010176</v>
+        <v>2.9916744</v>
       </c>
       <c r="N34">
-        <v>3.132655869387755</v>
+        <v>3.041999069387755</v>
       </c>
       <c r="O34">
-        <v>0.281939028244898</v>
+        <v>0.2737799162448979</v>
       </c>
       <c r="P34">
-        <v>2.850716841142857</v>
+        <v>2.768219153142857</v>
       </c>
       <c r="Q34">
-        <v>6.500716841142857</v>
+        <v>6.418219153142857</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09752684205693393</v>
+        <v>0.09825023435622532</v>
       </c>
       <c r="T34">
-        <v>0.7526885791685218</v>
+        <v>0.7632148185499203</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.079847247182421</v>
+        <v>2.016821573025378</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08859039701867095</v>
+        <v>0.09318306143862684</v>
       </c>
       <c r="C35">
-        <v>80.15815303760566</v>
+        <v>73.47114250336439</v>
       </c>
       <c r="D35">
-        <v>106.2261530376057</v>
+        <v>100.7351425033644</v>
       </c>
       <c r="E35">
-        <v>1.368000000000002</v>
+        <v>2.564</v>
       </c>
       <c r="F35">
-        <v>39.468</v>
+        <v>40.664</v>
       </c>
       <c r="G35">
         <v>13.4</v>
@@ -4157,45 +4157,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M35">
-        <v>2.9916744</v>
+        <v>3.65976</v>
       </c>
       <c r="N35">
-        <v>3.041999069387755</v>
+        <v>2.373913469387756</v>
       </c>
       <c r="O35">
-        <v>0.2737799162448979</v>
+        <v>0.213652212244898</v>
       </c>
       <c r="P35">
-        <v>2.768219153142857</v>
+        <v>2.160261257142858</v>
       </c>
       <c r="Q35">
-        <v>6.418219153142857</v>
+        <v>5.810261257142858</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09825023435622532</v>
+        <v>0.09899554763428312</v>
       </c>
       <c r="T35">
-        <v>0.7632148185499203</v>
+        <v>0.7740600348822705</v>
       </c>
       <c r="U35">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V35">
         <v>0.09</v>
       </c>
       <c r="W35">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.016821573025378</v>
+        <v>1.648652772145648</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09318306143862684</v>
+        <v>0.09351146585858272</v>
       </c>
       <c r="C36">
-        <v>73.47114250336439</v>
+        <v>71.90416822976934</v>
       </c>
       <c r="D36">
-        <v>100.7351425033644</v>
+        <v>100.3641682297693</v>
       </c>
       <c r="E36">
-        <v>2.564</v>
+        <v>3.759999999999998</v>
       </c>
       <c r="F36">
-        <v>40.664</v>
+        <v>41.86</v>
       </c>
       <c r="G36">
         <v>13.4</v>
@@ -4239,28 +4239,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M36">
-        <v>3.65976</v>
+        <v>3.7674</v>
       </c>
       <c r="N36">
-        <v>2.373913469387756</v>
+        <v>2.266273469387756</v>
       </c>
       <c r="O36">
-        <v>0.213652212244898</v>
+        <v>0.203964612244898</v>
       </c>
       <c r="P36">
-        <v>2.160261257142858</v>
+        <v>2.062308857142858</v>
       </c>
       <c r="Q36">
-        <v>5.810261257142858</v>
+        <v>5.712308857142858</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09899554763428312</v>
+        <v>0.09976379362858882</v>
       </c>
       <c r="T36">
-        <v>0.7740600348822705</v>
+        <v>0.7852389501786928</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.648652772145648</v>
+        <v>1.601548407227201</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09351146585858272</v>
+        <v>0.0938398702785386</v>
       </c>
       <c r="C37">
-        <v>71.90416822976934</v>
+        <v>70.33991628230163</v>
       </c>
       <c r="D37">
-        <v>100.3641682297693</v>
+        <v>99.99591628230164</v>
       </c>
       <c r="E37">
-        <v>3.759999999999998</v>
+        <v>4.956000000000003</v>
       </c>
       <c r="F37">
-        <v>41.86</v>
+        <v>43.056</v>
       </c>
       <c r="G37">
         <v>13.4</v>
@@ -4321,28 +4321,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M37">
-        <v>3.7674</v>
+        <v>3.87504</v>
       </c>
       <c r="N37">
-        <v>2.266273469387756</v>
+        <v>2.158633469387755</v>
       </c>
       <c r="O37">
-        <v>0.203964612244898</v>
+        <v>0.194277012244898</v>
       </c>
       <c r="P37">
-        <v>2.062308857142858</v>
+        <v>1.964356457142857</v>
       </c>
       <c r="Q37">
-        <v>5.712308857142858</v>
+        <v>5.614356457142858</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09976379362858882</v>
+        <v>0.1005560473102166</v>
       </c>
       <c r="T37">
-        <v>0.7852389501786928</v>
+        <v>0.7967672065781282</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.601548407227201</v>
+        <v>1.55706095147089</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09383987027853861</v>
+        <v>0.09416827469849451</v>
       </c>
       <c r="C38">
-        <v>70.33991628230163</v>
+        <v>68.77835680457852</v>
       </c>
       <c r="D38">
-        <v>99.99591628230162</v>
+        <v>99.63035680457851</v>
       </c>
       <c r="E38">
-        <v>4.955999999999996</v>
+        <v>6.151999999999994</v>
       </c>
       <c r="F38">
-        <v>43.056</v>
+        <v>44.252</v>
       </c>
       <c r="G38">
         <v>13.4</v>
@@ -4403,28 +4403,28 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M38">
-        <v>3.87504</v>
+        <v>3.982679999999999</v>
       </c>
       <c r="N38">
-        <v>2.158633469387756</v>
+        <v>2.050993469387756</v>
       </c>
       <c r="O38">
-        <v>0.194277012244898</v>
+        <v>0.1845894122448981</v>
       </c>
       <c r="P38">
-        <v>1.964356457142858</v>
+        <v>1.866404057142858</v>
       </c>
       <c r="Q38">
-        <v>5.614356457142858</v>
+        <v>5.516404057142858</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1005560473102166</v>
+        <v>0.1013734519023722</v>
       </c>
       <c r="T38">
-        <v>0.7967672065781281</v>
+        <v>0.8086614393711966</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.55706095147089</v>
+        <v>1.514978223052758</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09416827469849451</v>
+        <v>0.1147367531163581</v>
       </c>
       <c r="C39">
-        <v>68.77835680457852</v>
+        <v>49.02051130112252</v>
       </c>
       <c r="D39">
-        <v>99.63035680457851</v>
+        <v>81.06851130112251</v>
       </c>
       <c r="E39">
-        <v>6.151999999999994</v>
+        <v>7.347999999999999</v>
       </c>
       <c r="F39">
-        <v>44.252</v>
+        <v>45.448</v>
       </c>
       <c r="G39">
         <v>13.4</v>
@@ -4485,45 +4485,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M39">
-        <v>3.982679999999999</v>
+        <v>6.671766400000001</v>
       </c>
       <c r="N39">
-        <v>2.050993469387756</v>
+        <v>-0.6380929306122454</v>
       </c>
       <c r="O39">
-        <v>0.1845894122448981</v>
+        <v>-0.05742836375510208</v>
       </c>
       <c r="P39">
-        <v>1.866404057142858</v>
+        <v>-0.5806645668571433</v>
       </c>
       <c r="Q39">
-        <v>5.516404057142858</v>
+        <v>3.069335433142856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1013734519023722</v>
+        <v>0.1024082949207213</v>
       </c>
       <c r="T39">
-        <v>0.8086614393711966</v>
+        <v>0.8237196662060432</v>
       </c>
       <c r="U39">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.09</v>
+        <v>0.08139232996000847</v>
       </c>
       <c r="W39">
-        <v>0.0819</v>
+        <v>0.1348516059618708</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.514978223052758</v>
+        <v>0.904359221777872</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1147367531163581</v>
+        <v>0.1157467531163581</v>
       </c>
       <c r="C40">
-        <v>49.02051130112252</v>
+        <v>47.08958158781628</v>
       </c>
       <c r="D40">
-        <v>81.06851130112251</v>
+        <v>80.33358158781627</v>
       </c>
       <c r="E40">
-        <v>7.347999999999999</v>
+        <v>8.543999999999997</v>
       </c>
       <c r="F40">
-        <v>45.448</v>
+        <v>46.644</v>
       </c>
       <c r="G40">
         <v>13.4</v>
@@ -4567,37 +4567,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M40">
-        <v>6.671766400000001</v>
+        <v>6.8473392</v>
       </c>
       <c r="N40">
-        <v>-0.6380929306122454</v>
+        <v>-0.8136657306122448</v>
       </c>
       <c r="O40">
-        <v>-0.05742836375510208</v>
+        <v>-0.07322991575510203</v>
       </c>
       <c r="P40">
-        <v>-0.5806645668571433</v>
+        <v>-0.7404358148571427</v>
       </c>
       <c r="Q40">
-        <v>3.069335433142856</v>
+        <v>2.909564185142857</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1024082949207213</v>
+        <v>0.1033362997554872</v>
       </c>
       <c r="T40">
-        <v>0.8237196662060432</v>
+        <v>0.8372232672913882</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.08139232996000847</v>
+        <v>0.07930534714052108</v>
       </c>
       <c r="W40">
-        <v>0.1348516059618708</v>
+        <v>0.1351579750397715</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.904359221777872</v>
+        <v>0.8811705237835676</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1157467531163581</v>
+        <v>0.1167567531163581</v>
       </c>
       <c r="C41">
-        <v>47.08958158781628</v>
+        <v>45.17185722814312</v>
       </c>
       <c r="D41">
-        <v>80.33358158781627</v>
+        <v>79.61185722814312</v>
       </c>
       <c r="E41">
-        <v>8.543999999999997</v>
+        <v>9.740000000000002</v>
       </c>
       <c r="F41">
-        <v>46.644</v>
+        <v>47.84</v>
       </c>
       <c r="G41">
         <v>13.4</v>
@@ -4649,37 +4649,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M41">
-        <v>6.8473392</v>
+        <v>7.022912000000002</v>
       </c>
       <c r="N41">
-        <v>-0.8136657306122448</v>
+        <v>-0.989238530612246</v>
       </c>
       <c r="O41">
-        <v>-0.07322991575510203</v>
+        <v>-0.08903146775510214</v>
       </c>
       <c r="P41">
-        <v>-0.7404358148571427</v>
+        <v>-0.9002070628571438</v>
       </c>
       <c r="Q41">
-        <v>2.909564185142857</v>
+        <v>2.749792937142856</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1033362997554872</v>
+        <v>0.1042952380847453</v>
       </c>
       <c r="T41">
-        <v>0.8372232672913882</v>
+        <v>0.8511769884129112</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.07930534714052108</v>
+        <v>0.07732271346200804</v>
       </c>
       <c r="W41">
-        <v>0.1351579750397715</v>
+        <v>0.1354490256637772</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8811705237835676</v>
+        <v>0.8591412606889783</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1167567531163581</v>
+        <v>0.1177667531163581</v>
       </c>
       <c r="C42">
-        <v>45.17185722814312</v>
+        <v>43.26698547682811</v>
       </c>
       <c r="D42">
-        <v>79.61185722814312</v>
+        <v>78.90298547682811</v>
       </c>
       <c r="E42">
-        <v>9.740000000000002</v>
+        <v>10.936</v>
       </c>
       <c r="F42">
-        <v>47.84</v>
+        <v>49.036</v>
       </c>
       <c r="G42">
         <v>13.4</v>
@@ -4731,37 +4731,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M42">
-        <v>7.022912000000002</v>
+        <v>7.198484800000001</v>
       </c>
       <c r="N42">
-        <v>-0.989238530612246</v>
+        <v>-1.164811330612245</v>
       </c>
       <c r="O42">
-        <v>-0.08903146775510214</v>
+        <v>-0.1048330197551021</v>
       </c>
       <c r="P42">
-        <v>-0.9002070628571438</v>
+        <v>-1.059978310857143</v>
       </c>
       <c r="Q42">
-        <v>2.749792937142856</v>
+        <v>2.590021689142857</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1042952380847453</v>
+        <v>0.1052866827980461</v>
       </c>
       <c r="T42">
-        <v>0.8511769884129112</v>
+        <v>0.8656037170300793</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.07732271346200804</v>
+        <v>0.07543679362147127</v>
       </c>
       <c r="W42">
-        <v>0.1354490256637772</v>
+        <v>0.135725878696368</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8591412606889783</v>
+        <v>0.8381865957941252</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1177667531163581</v>
+        <v>0.1187767531163581</v>
       </c>
       <c r="C43">
-        <v>43.26698547682811</v>
+        <v>41.37462604123027</v>
       </c>
       <c r="D43">
-        <v>78.90298547682811</v>
+        <v>78.20662604123027</v>
       </c>
       <c r="E43">
-        <v>10.936</v>
+        <v>12.132</v>
       </c>
       <c r="F43">
-        <v>49.036</v>
+        <v>50.232</v>
       </c>
       <c r="G43">
         <v>13.4</v>
@@ -4813,37 +4813,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M43">
-        <v>7.198484800000001</v>
+        <v>7.3740576</v>
       </c>
       <c r="N43">
-        <v>-1.164811330612245</v>
+        <v>-1.340384130612245</v>
       </c>
       <c r="O43">
-        <v>-0.1048330197551021</v>
+        <v>-0.120634571755102</v>
       </c>
       <c r="P43">
-        <v>-1.059978310857143</v>
+        <v>-1.219749558857143</v>
       </c>
       <c r="Q43">
-        <v>2.590021689142857</v>
+        <v>2.430250441142857</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1052866827980461</v>
+        <v>0.1063123152600813</v>
       </c>
       <c r="T43">
-        <v>0.8656037170300793</v>
+        <v>0.8805279190478391</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.07543679362147127</v>
+        <v>0.07364067948762673</v>
       </c>
       <c r="W43">
-        <v>0.135725878696368</v>
+        <v>0.1359895482512164</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8381865957941252</v>
+        <v>0.8182297720847413</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1187767531163581</v>
+        <v>0.1433079935979372</v>
       </c>
       <c r="C44">
-        <v>41.37462604123028</v>
+        <v>26.37366304178424</v>
       </c>
       <c r="D44">
-        <v>78.20662604123027</v>
+        <v>64.40166304178423</v>
       </c>
       <c r="E44">
-        <v>12.13199999999999</v>
+        <v>13.328</v>
       </c>
       <c r="F44">
-        <v>50.23199999999999</v>
+        <v>51.428</v>
       </c>
       <c r="G44">
         <v>13.4</v>
@@ -4895,45 +4895,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M44">
-        <v>7.3740576</v>
+        <v>10.3267424</v>
       </c>
       <c r="N44">
-        <v>-1.340384130612244</v>
+        <v>-4.293068930612245</v>
       </c>
       <c r="O44">
-        <v>-0.1206345717551019</v>
+        <v>-0.386376203755102</v>
       </c>
       <c r="P44">
-        <v>-1.219749558857142</v>
+        <v>-3.906692726857143</v>
       </c>
       <c r="Q44">
-        <v>2.430250441142858</v>
+        <v>-0.2566927268571431</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1063123152600813</v>
+        <v>0.1079024268989936</v>
       </c>
       <c r="T44">
-        <v>0.8805279190478391</v>
+        <v>0.9036659808861173</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.07364067948762673</v>
+        <v>0.05258488991115901</v>
       </c>
       <c r="W44">
-        <v>0.1359895482512164</v>
+        <v>0.1902409541058393</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8182297720847416</v>
+        <v>0.5842765545684334</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1433079935979372</v>
+        <v>0.1448579935979372</v>
       </c>
       <c r="C45">
-        <v>26.37366304178424</v>
+        <v>24.4672941114743</v>
       </c>
       <c r="D45">
-        <v>64.40166304178423</v>
+        <v>63.6912941114743</v>
       </c>
       <c r="E45">
-        <v>13.328</v>
+        <v>14.52399999999999</v>
       </c>
       <c r="F45">
-        <v>51.428</v>
+        <v>52.624</v>
       </c>
       <c r="G45">
         <v>13.4</v>
@@ -4977,37 +4977,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M45">
-        <v>10.3267424</v>
+        <v>10.5668992</v>
       </c>
       <c r="N45">
-        <v>-4.293068930612245</v>
+        <v>-4.533225730612244</v>
       </c>
       <c r="O45">
-        <v>-0.386376203755102</v>
+        <v>-0.407990315755102</v>
       </c>
       <c r="P45">
-        <v>-3.906692726857143</v>
+        <v>-4.125235414857142</v>
       </c>
       <c r="Q45">
-        <v>-0.2566927268571431</v>
+        <v>-0.4752354148571425</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1079024268989936</v>
+        <v>0.1090113988079042</v>
       </c>
       <c r="T45">
-        <v>0.9036659808861173</v>
+        <v>0.9198028734019408</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05258488991115901</v>
+        <v>0.05138977877681448</v>
       </c>
       <c r="W45">
-        <v>0.1902409541058393</v>
+        <v>0.1904809324216157</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5842765545684334</v>
+        <v>0.5709975419646054</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1448579935979372</v>
+        <v>0.1464079935979372</v>
       </c>
       <c r="C46">
-        <v>24.4672941114743</v>
+        <v>22.57642535837785</v>
       </c>
       <c r="D46">
-        <v>63.6912941114743</v>
+        <v>62.99642535837786</v>
       </c>
       <c r="E46">
-        <v>14.52399999999999</v>
+        <v>15.72</v>
       </c>
       <c r="F46">
-        <v>52.624</v>
+        <v>53.82</v>
       </c>
       <c r="G46">
         <v>13.4</v>
@@ -5059,37 +5059,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M46">
-        <v>10.5668992</v>
+        <v>10.807056</v>
       </c>
       <c r="N46">
-        <v>-4.533225730612244</v>
+        <v>-4.773382530612245</v>
       </c>
       <c r="O46">
-        <v>-0.407990315755102</v>
+        <v>-0.4296044277551021</v>
       </c>
       <c r="P46">
-        <v>-4.125235414857142</v>
+        <v>-4.343778102857144</v>
       </c>
       <c r="Q46">
-        <v>-0.4752354148571425</v>
+        <v>-0.6937781028571437</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1090113988079042</v>
+        <v>0.1101606969680479</v>
       </c>
       <c r="T46">
-        <v>0.9198028734019408</v>
+        <v>0.9365265620092488</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05138977877681448</v>
+        <v>0.05024778369288527</v>
       </c>
       <c r="W46">
-        <v>0.1904809324216157</v>
+        <v>0.1907102450344687</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5709975419646054</v>
+        <v>0.5583087076987252</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1464079935979372</v>
+        <v>0.1479579935979372</v>
       </c>
       <c r="C47">
-        <v>22.57642535837785</v>
+        <v>20.700554939164</v>
       </c>
       <c r="D47">
-        <v>62.99642535837786</v>
+        <v>62.31655493916399</v>
       </c>
       <c r="E47">
-        <v>15.72</v>
+        <v>16.916</v>
       </c>
       <c r="F47">
-        <v>53.82</v>
+        <v>55.016</v>
       </c>
       <c r="G47">
         <v>13.4</v>
@@ -5141,37 +5141,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M47">
-        <v>10.807056</v>
+        <v>11.0472128</v>
       </c>
       <c r="N47">
-        <v>-4.773382530612245</v>
+        <v>-5.013539330612245</v>
       </c>
       <c r="O47">
-        <v>-0.4296044277551021</v>
+        <v>-0.451218539755102</v>
       </c>
       <c r="P47">
-        <v>-4.343778102857144</v>
+        <v>-4.562320790857143</v>
       </c>
       <c r="Q47">
-        <v>-0.6937781028571437</v>
+        <v>-0.9123207908571431</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1101606969680479</v>
+        <v>0.1113525617267154</v>
       </c>
       <c r="T47">
-        <v>0.9365265620092488</v>
+        <v>0.9538696464909016</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.05024778369288527</v>
+        <v>0.0491554405691269</v>
       </c>
       <c r="W47">
-        <v>0.1907102450344687</v>
+        <v>0.1909295875337193</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5583087076987252</v>
+        <v>0.5461715618791878</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1479579935979372</v>
+        <v>0.1495079935979372</v>
       </c>
       <c r="C48">
-        <v>20.700554939164</v>
+        <v>18.83920244318284</v>
       </c>
       <c r="D48">
-        <v>62.31655493916399</v>
+        <v>61.65120244318285</v>
       </c>
       <c r="E48">
-        <v>16.916</v>
+        <v>18.112</v>
       </c>
       <c r="F48">
-        <v>55.016</v>
+        <v>56.212</v>
       </c>
       <c r="G48">
         <v>13.4</v>
@@ -5223,37 +5223,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M48">
-        <v>11.0472128</v>
+        <v>11.2873696</v>
       </c>
       <c r="N48">
-        <v>-5.013539330612245</v>
+        <v>-5.253696130612246</v>
       </c>
       <c r="O48">
-        <v>-0.451218539755102</v>
+        <v>-0.4728326517551021</v>
       </c>
       <c r="P48">
-        <v>-4.562320790857143</v>
+        <v>-4.780863478857144</v>
       </c>
       <c r="Q48">
-        <v>-0.9123207908571431</v>
+        <v>-1.130863478857144</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1113525617267154</v>
+        <v>0.1125894025140119</v>
       </c>
       <c r="T48">
-        <v>0.9538696464909016</v>
+        <v>0.9718671869907298</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.0491554405691269</v>
+        <v>0.04810958013148589</v>
       </c>
       <c r="W48">
-        <v>0.1909295875337193</v>
+        <v>0.1911395963095976</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5461715618791878</v>
+        <v>0.5345508903498433</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1495079935979372</v>
+        <v>0.1510579935979372</v>
       </c>
       <c r="C49">
-        <v>18.83920244318284</v>
+        <v>16.99190776037176</v>
       </c>
       <c r="D49">
-        <v>61.65120244318285</v>
+        <v>60.99990776037176</v>
       </c>
       <c r="E49">
-        <v>18.112</v>
+        <v>19.308</v>
       </c>
       <c r="F49">
-        <v>56.212</v>
+        <v>57.408</v>
       </c>
       <c r="G49">
         <v>13.4</v>
@@ -5305,37 +5305,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M49">
-        <v>11.2873696</v>
+        <v>11.5275264</v>
       </c>
       <c r="N49">
-        <v>-5.253696130612246</v>
+        <v>-5.493852930612245</v>
       </c>
       <c r="O49">
-        <v>-0.4728326517551021</v>
+        <v>-0.494446763755102</v>
       </c>
       <c r="P49">
-        <v>-4.780863478857144</v>
+        <v>-4.999406166857144</v>
       </c>
       <c r="Q49">
-        <v>-1.130863478857144</v>
+        <v>-1.349406166857144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1125894025140119</v>
+        <v>0.1138738141008199</v>
       </c>
       <c r="T49">
-        <v>0.9718671869907298</v>
+        <v>0.9905569405867055</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.04810958013148589</v>
+        <v>0.04710729721207994</v>
       </c>
       <c r="W49">
-        <v>0.1911395963095976</v>
+        <v>0.1913408547198144</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5345508903498433</v>
+        <v>0.5234144134675549</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1510579935979372</v>
+        <v>0.1526079935979372</v>
       </c>
       <c r="C50">
-        <v>16.99190776037178</v>
+        <v>15.15823002016894</v>
       </c>
       <c r="D50">
-        <v>60.99990776037177</v>
+        <v>60.36223002016894</v>
       </c>
       <c r="E50">
-        <v>19.30799999999999</v>
+        <v>20.504</v>
       </c>
       <c r="F50">
-        <v>57.40799999999999</v>
+        <v>58.604</v>
       </c>
       <c r="G50">
         <v>13.4</v>
@@ -5387,37 +5387,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M50">
-        <v>11.5275264</v>
+        <v>11.7676832</v>
       </c>
       <c r="N50">
-        <v>-5.493852930612244</v>
+        <v>-5.734009730612245</v>
       </c>
       <c r="O50">
-        <v>-0.4944467637551019</v>
+        <v>-0.5160608757551021</v>
       </c>
       <c r="P50">
-        <v>-4.999406166857142</v>
+        <v>-5.217948854857143</v>
       </c>
       <c r="Q50">
-        <v>-1.349406166857142</v>
+        <v>-1.567948854857143</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1138738141008199</v>
+        <v>0.1152085947694634</v>
       </c>
       <c r="T50">
-        <v>0.9905569405867054</v>
+        <v>1.009979625696249</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.04710729721207995</v>
+        <v>0.04614592379958852</v>
       </c>
       <c r="W50">
-        <v>0.1913408547198144</v>
+        <v>0.1915338985010426</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.523414413467555</v>
+        <v>0.5127324866620946</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1526079935979372</v>
+        <v>0.1541579935979372</v>
       </c>
       <c r="C51">
-        <v>15.15823002016894</v>
+        <v>13.33774659629267</v>
       </c>
       <c r="D51">
-        <v>60.36223002016894</v>
+        <v>59.73774659629267</v>
       </c>
       <c r="E51">
-        <v>20.504</v>
+        <v>21.7</v>
       </c>
       <c r="F51">
-        <v>58.604</v>
+        <v>59.8</v>
       </c>
       <c r="G51">
         <v>13.4</v>
@@ -5469,37 +5469,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M51">
-        <v>11.7676832</v>
+        <v>12.00784</v>
       </c>
       <c r="N51">
-        <v>-5.734009730612245</v>
+        <v>-5.974166530612244</v>
       </c>
       <c r="O51">
-        <v>-0.5160608757551021</v>
+        <v>-0.5376749877551019</v>
       </c>
       <c r="P51">
-        <v>-5.217948854857143</v>
+        <v>-5.436491542857143</v>
       </c>
       <c r="Q51">
-        <v>-1.567948854857143</v>
+        <v>-1.786491542857143</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1152085947694634</v>
+        <v>0.1165967666648527</v>
       </c>
       <c r="T51">
-        <v>1.009979625696249</v>
+        <v>1.030179218210174</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.04614592379958852</v>
+        <v>0.04522300532359676</v>
       </c>
       <c r="W51">
-        <v>0.1915338985010426</v>
+        <v>0.1917192205310218</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5127324866620946</v>
+        <v>0.5024778369288527</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1541579935979372</v>
+        <v>0.1736795477708359</v>
       </c>
       <c r="C52">
-        <v>13.33774659629267</v>
+        <v>5.255316532375758</v>
       </c>
       <c r="D52">
-        <v>59.73774659629267</v>
+        <v>52.85131653237575</v>
       </c>
       <c r="E52">
-        <v>21.7</v>
+        <v>22.89599999999999</v>
       </c>
       <c r="F52">
-        <v>59.8</v>
+        <v>60.996</v>
       </c>
       <c r="G52">
         <v>13.4</v>
@@ -5551,45 +5551,45 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M52">
-        <v>12.00784</v>
+        <v>14.3828568</v>
       </c>
       <c r="N52">
-        <v>-5.974166530612244</v>
+        <v>-8.349183330612243</v>
       </c>
       <c r="O52">
-        <v>-0.5376749877551019</v>
+        <v>-0.7514264997551019</v>
       </c>
       <c r="P52">
-        <v>-5.436491542857143</v>
+        <v>-7.597756830857142</v>
       </c>
       <c r="Q52">
-        <v>-1.786491542857143</v>
+        <v>-3.947756830857142</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1165967666648527</v>
+        <v>0.1182896683782143</v>
       </c>
       <c r="T52">
-        <v>1.030179218210174</v>
+        <v>1.054813000877588</v>
       </c>
       <c r="U52">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04522300532359676</v>
+        <v>0.03775540699570186</v>
       </c>
       <c r="W52">
-        <v>0.1917192205310218</v>
+        <v>0.2268972750304135</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5024778369288527</v>
+        <v>0.4195045221744651</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1736795477708359</v>
+        <v>0.1755795477708359</v>
       </c>
       <c r="C53">
-        <v>5.255316532375758</v>
+        <v>3.472915443841906</v>
       </c>
       <c r="D53">
-        <v>52.85131653237575</v>
+        <v>52.2649154438419</v>
       </c>
       <c r="E53">
-        <v>22.89599999999999</v>
+        <v>24.092</v>
       </c>
       <c r="F53">
-        <v>60.996</v>
+        <v>62.192</v>
       </c>
       <c r="G53">
         <v>13.4</v>
@@ -5633,37 +5633,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M53">
-        <v>14.3828568</v>
+        <v>14.6648736</v>
       </c>
       <c r="N53">
-        <v>-8.349183330612243</v>
+        <v>-8.631200130612244</v>
       </c>
       <c r="O53">
-        <v>-0.7514264997551019</v>
+        <v>-0.7768080117551019</v>
       </c>
       <c r="P53">
-        <v>-7.597756830857142</v>
+        <v>-7.854392118857143</v>
       </c>
       <c r="Q53">
-        <v>-3.947756830857142</v>
+        <v>-4.204392118857143</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1182896683782143</v>
+        <v>0.1197998698027605</v>
       </c>
       <c r="T53">
-        <v>1.054813000877588</v>
+        <v>1.076788271729204</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03775540699570186</v>
+        <v>0.03702934147655374</v>
       </c>
       <c r="W53">
-        <v>0.2268972750304135</v>
+        <v>0.2270684812798286</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4195045221744651</v>
+        <v>0.4114371275172638</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1755795477708359</v>
+        <v>0.1774795477708359</v>
       </c>
       <c r="C54">
-        <v>3.472915443841906</v>
+        <v>1.703384150349571</v>
       </c>
       <c r="D54">
-        <v>52.2649154438419</v>
+        <v>51.69138415034957</v>
       </c>
       <c r="E54">
-        <v>24.092</v>
+        <v>25.288</v>
       </c>
       <c r="F54">
-        <v>62.192</v>
+        <v>63.388</v>
       </c>
       <c r="G54">
         <v>13.4</v>
@@ -5715,37 +5715,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M54">
-        <v>14.6648736</v>
+        <v>14.9468904</v>
       </c>
       <c r="N54">
-        <v>-8.631200130612244</v>
+        <v>-8.913216930612245</v>
       </c>
       <c r="O54">
-        <v>-0.7768080117551019</v>
+        <v>-0.802189523755102</v>
       </c>
       <c r="P54">
-        <v>-7.854392118857143</v>
+        <v>-8.111027406857144</v>
       </c>
       <c r="Q54">
-        <v>-4.204392118857143</v>
+        <v>-4.461027406857143</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1197998698027605</v>
+        <v>0.1213743351177128</v>
       </c>
       <c r="T54">
-        <v>1.076788271729204</v>
+        <v>1.0996986604894</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03702934147655374</v>
+        <v>0.03633067465624141</v>
       </c>
       <c r="W54">
-        <v>0.2270684812798286</v>
+        <v>0.2272332269160583</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4114371275172638</v>
+        <v>0.4036741628471268</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1774795477708359</v>
+        <v>0.1793795477708359</v>
       </c>
       <c r="C55">
-        <v>1.703384150349571</v>
+        <v>-0.05369643102208954</v>
       </c>
       <c r="D55">
-        <v>51.69138415034957</v>
+        <v>51.13030356897791</v>
       </c>
       <c r="E55">
-        <v>25.288</v>
+        <v>26.484</v>
       </c>
       <c r="F55">
-        <v>63.388</v>
+        <v>64.584</v>
       </c>
       <c r="G55">
         <v>13.4</v>
@@ -5797,37 +5797,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M55">
-        <v>14.9468904</v>
+        <v>15.2289072</v>
       </c>
       <c r="N55">
-        <v>-8.913216930612245</v>
+        <v>-9.195233730612246</v>
       </c>
       <c r="O55">
-        <v>-0.802189523755102</v>
+        <v>-0.8275710357551022</v>
       </c>
       <c r="P55">
-        <v>-8.111027406857144</v>
+        <v>-8.367662694857144</v>
       </c>
       <c r="Q55">
-        <v>-4.461027406857143</v>
+        <v>-4.717662694857143</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1213743351177128</v>
+        <v>0.1230172554463588</v>
       </c>
       <c r="T55">
-        <v>1.0996986604894</v>
+        <v>1.123605153108735</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03633067465624141</v>
+        <v>0.03565788438482952</v>
       </c>
       <c r="W55">
-        <v>0.2272332269160583</v>
+        <v>0.2273918708620572</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4036741628471268</v>
+        <v>0.3961987153869947</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1793795477708359</v>
+        <v>0.1812795477708359</v>
       </c>
       <c r="C56">
-        <v>-0.05369643102208954</v>
+        <v>-1.798727382949153</v>
       </c>
       <c r="D56">
-        <v>51.13030356897791</v>
+        <v>50.58127261705085</v>
       </c>
       <c r="E56">
-        <v>26.484</v>
+        <v>27.68</v>
       </c>
       <c r="F56">
-        <v>64.584</v>
+        <v>65.78</v>
       </c>
       <c r="G56">
         <v>13.4</v>
@@ -5879,37 +5879,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M56">
-        <v>15.2289072</v>
+        <v>15.510924</v>
       </c>
       <c r="N56">
-        <v>-9.195233730612246</v>
+        <v>-9.477250530612245</v>
       </c>
       <c r="O56">
-        <v>-0.8275710357551022</v>
+        <v>-0.8529525477551021</v>
       </c>
       <c r="P56">
-        <v>-8.367662694857144</v>
+        <v>-8.624297982857144</v>
       </c>
       <c r="Q56">
-        <v>-4.717662694857143</v>
+        <v>-4.974297982857143</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1230172554463588</v>
+        <v>0.1247331944562779</v>
       </c>
       <c r="T56">
-        <v>1.123605153108735</v>
+        <v>1.148574156511151</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03565788438482952</v>
+        <v>0.03500955921419626</v>
       </c>
       <c r="W56">
-        <v>0.2273918708620572</v>
+        <v>0.2275447459372925</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3961987153869947</v>
+        <v>0.3889951023799585</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1812795477708359</v>
+        <v>0.1831795477708359</v>
       </c>
       <c r="C57">
-        <v>-1.798727382949153</v>
+        <v>-3.532092744017966</v>
       </c>
       <c r="D57">
-        <v>50.58127261705085</v>
+        <v>50.04390725598203</v>
       </c>
       <c r="E57">
-        <v>27.68</v>
+        <v>28.876</v>
       </c>
       <c r="F57">
-        <v>65.78</v>
+        <v>66.976</v>
       </c>
       <c r="G57">
         <v>13.4</v>
@@ -5961,37 +5961,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M57">
-        <v>15.510924</v>
+        <v>15.7929408</v>
       </c>
       <c r="N57">
-        <v>-9.477250530612245</v>
+        <v>-9.759267330612245</v>
       </c>
       <c r="O57">
-        <v>-0.8529525477551021</v>
+        <v>-0.878334059755102</v>
       </c>
       <c r="P57">
-        <v>-8.624297982857144</v>
+        <v>-8.880933270857142</v>
       </c>
       <c r="Q57">
-        <v>-4.974297982857143</v>
+        <v>-5.230933270857141</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1247331944562779</v>
+        <v>0.1265271306939205</v>
       </c>
       <c r="T57">
-        <v>1.148574156511151</v>
+        <v>1.174678114613677</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03500955921419626</v>
+        <v>0.03438438851394276</v>
       </c>
       <c r="W57">
-        <v>0.2275447459372925</v>
+        <v>0.2276921611884123</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3889951023799585</v>
+        <v>0.3820487612660307</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1831795477708359</v>
+        <v>0.185079547770836</v>
       </c>
       <c r="C58">
-        <v>-3.532092744017966</v>
+        <v>-5.254160404572922</v>
       </c>
       <c r="D58">
-        <v>50.04390725598203</v>
+        <v>49.51783959542709</v>
       </c>
       <c r="E58">
-        <v>28.876</v>
+        <v>30.07200000000001</v>
       </c>
       <c r="F58">
-        <v>66.976</v>
+        <v>68.17200000000001</v>
       </c>
       <c r="G58">
         <v>13.4</v>
@@ -6043,37 +6043,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M58">
-        <v>15.7929408</v>
+        <v>16.0749576</v>
       </c>
       <c r="N58">
-        <v>-9.759267330612245</v>
+        <v>-10.04128413061225</v>
       </c>
       <c r="O58">
-        <v>-0.878334059755102</v>
+        <v>-0.9037155717551024</v>
       </c>
       <c r="P58">
-        <v>-8.880933270857142</v>
+        <v>-9.137568558857147</v>
       </c>
       <c r="Q58">
-        <v>-5.230933270857141</v>
+        <v>-5.487568558857147</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1265271306939205</v>
+        <v>0.1284045058263373</v>
       </c>
       <c r="T58">
-        <v>1.174678114613677</v>
+        <v>1.201996210302368</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03438438851394276</v>
+        <v>0.03378115362773323</v>
       </c>
       <c r="W58">
-        <v>0.2276921611884123</v>
+        <v>0.2278344039745805</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3820487612660307</v>
+        <v>0.3753461514192581</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.185079547770836</v>
+        <v>0.1869795477708359</v>
       </c>
       <c r="C59">
-        <v>-5.254160404572922</v>
+        <v>-6.965282946648415</v>
       </c>
       <c r="D59">
-        <v>49.51783959542709</v>
+        <v>49.0027170533516</v>
       </c>
       <c r="E59">
-        <v>30.07200000000001</v>
+        <v>31.26800000000001</v>
       </c>
       <c r="F59">
-        <v>68.17200000000001</v>
+        <v>69.36800000000001</v>
       </c>
       <c r="G59">
         <v>13.4</v>
@@ -6125,37 +6125,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M59">
-        <v>16.0749576</v>
+        <v>16.3569744</v>
       </c>
       <c r="N59">
-        <v>-10.04128413061225</v>
+        <v>-10.32330093061225</v>
       </c>
       <c r="O59">
-        <v>-0.9037155717551024</v>
+        <v>-0.9290970837551021</v>
       </c>
       <c r="P59">
-        <v>-9.137568558857147</v>
+        <v>-9.394203846857144</v>
       </c>
       <c r="Q59">
-        <v>-5.487568558857147</v>
+        <v>-5.744203846857143</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1284045058263373</v>
+        <v>0.1303712797745834</v>
       </c>
       <c r="T59">
-        <v>1.201996210302368</v>
+        <v>1.230615167690519</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03378115362773323</v>
+        <v>0.03319871994449645</v>
       </c>
       <c r="W59">
-        <v>0.2278344039745805</v>
+        <v>0.2279717418370878</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3753461514192581</v>
+        <v>0.3688746660499607</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1869795477708359</v>
+        <v>0.1888795477708359</v>
       </c>
       <c r="C60">
-        <v>-6.965282946648387</v>
+        <v>-8.665798432014959</v>
       </c>
       <c r="D60">
-        <v>49.00271705335161</v>
+        <v>48.49820156798503</v>
       </c>
       <c r="E60">
-        <v>31.26799999999999</v>
+        <v>32.46399999999999</v>
       </c>
       <c r="F60">
-        <v>69.36799999999999</v>
+        <v>70.56399999999999</v>
       </c>
       <c r="G60">
         <v>13.4</v>
@@ -6207,37 +6207,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M60">
-        <v>16.3569744</v>
+        <v>16.6389912</v>
       </c>
       <c r="N60">
-        <v>-10.32330093061224</v>
+        <v>-10.60531773061224</v>
       </c>
       <c r="O60">
-        <v>-0.9290970837551018</v>
+        <v>-0.954478595755102</v>
       </c>
       <c r="P60">
-        <v>-9.394203846857142</v>
+        <v>-9.650839134857142</v>
       </c>
       <c r="Q60">
-        <v>-5.744203846857141</v>
+        <v>-6.000839134857141</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1303712797745834</v>
+        <v>0.1324339939154269</v>
       </c>
       <c r="T60">
-        <v>1.230615167690519</v>
+        <v>1.260630171780532</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03319871994449646</v>
+        <v>0.03263602977594567</v>
       </c>
       <c r="W60">
-        <v>0.2279717418370878</v>
+        <v>0.228104424178832</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3688746660499607</v>
+        <v>0.3626225530660631</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1888795477708359</v>
+        <v>0.1907795477708359</v>
       </c>
       <c r="C61">
-        <v>-8.665798432014959</v>
+        <v>-10.35603114204054</v>
       </c>
       <c r="D61">
-        <v>48.49820156798503</v>
+        <v>48.00396885795945</v>
       </c>
       <c r="E61">
-        <v>32.46399999999999</v>
+        <v>33.65999999999999</v>
       </c>
       <c r="F61">
-        <v>70.56399999999999</v>
+        <v>71.75999999999999</v>
       </c>
       <c r="G61">
         <v>13.4</v>
@@ -6289,37 +6289,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M61">
-        <v>16.6389912</v>
+        <v>16.921008</v>
       </c>
       <c r="N61">
-        <v>-10.60531773061224</v>
+        <v>-10.88733453061224</v>
       </c>
       <c r="O61">
-        <v>-0.954478595755102</v>
+        <v>-0.9798601077551017</v>
       </c>
       <c r="P61">
-        <v>-9.650839134857142</v>
+        <v>-9.90747442285714</v>
       </c>
       <c r="Q61">
-        <v>-6.000839134857141</v>
+        <v>-6.25747442285714</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1324339939154269</v>
+        <v>0.1345998437633126</v>
       </c>
       <c r="T61">
-        <v>1.260630171780532</v>
+        <v>1.292145926075045</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03263602977594567</v>
+        <v>0.03209209594634658</v>
       </c>
       <c r="W61">
-        <v>0.228104424178832</v>
+        <v>0.2282326837758515</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3626225530660631</v>
+        <v>0.3565788438482954</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1907795477708359</v>
+        <v>0.192679547770836</v>
       </c>
       <c r="C62">
-        <v>-10.35603114204054</v>
+        <v>-12.03629227276991</v>
       </c>
       <c r="D62">
-        <v>48.00396885795945</v>
+        <v>47.51970772723008</v>
       </c>
       <c r="E62">
-        <v>33.65999999999999</v>
+        <v>34.85599999999999</v>
       </c>
       <c r="F62">
-        <v>71.75999999999999</v>
+        <v>72.95599999999999</v>
       </c>
       <c r="G62">
         <v>13.4</v>
@@ -6371,37 +6371,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M62">
-        <v>16.921008</v>
+        <v>17.2030248</v>
       </c>
       <c r="N62">
-        <v>-10.88733453061224</v>
+        <v>-11.16935133061224</v>
       </c>
       <c r="O62">
-        <v>-0.9798601077551017</v>
+        <v>-1.005241619755102</v>
       </c>
       <c r="P62">
-        <v>-9.90747442285714</v>
+        <v>-10.16410971085714</v>
       </c>
       <c r="Q62">
-        <v>-6.25747442285714</v>
+        <v>-6.51410971085714</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1345998437633126</v>
+        <v>0.1368767628341667</v>
       </c>
       <c r="T62">
-        <v>1.292145926075045</v>
+        <v>1.325277872897482</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03209209594634658</v>
+        <v>0.03156599601279991</v>
       </c>
       <c r="W62">
-        <v>0.2282326837758515</v>
+        <v>0.2283567381401818</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3565788438482954</v>
+        <v>0.3507332890311102</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.192679547770836</v>
+        <v>0.1945795477708359</v>
       </c>
       <c r="C63">
-        <v>-12.03629227276991</v>
+        <v>-13.70688058835258</v>
       </c>
       <c r="D63">
-        <v>47.51970772723008</v>
+        <v>47.04511941164742</v>
       </c>
       <c r="E63">
-        <v>34.85599999999999</v>
+        <v>36.052</v>
       </c>
       <c r="F63">
-        <v>72.95599999999999</v>
+        <v>74.152</v>
       </c>
       <c r="G63">
         <v>13.4</v>
@@ -6453,37 +6453,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M63">
-        <v>17.2030248</v>
+        <v>17.4850416</v>
       </c>
       <c r="N63">
-        <v>-11.16935133061224</v>
+        <v>-11.45136813061225</v>
       </c>
       <c r="O63">
-        <v>-1.005241619755102</v>
+        <v>-1.030623131755102</v>
       </c>
       <c r="P63">
-        <v>-10.16410971085714</v>
+        <v>-10.42074499885715</v>
       </c>
       <c r="Q63">
-        <v>-6.51410971085714</v>
+        <v>-6.770744998857145</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1368767628341667</v>
+        <v>0.1392735197508554</v>
       </c>
       <c r="T63">
-        <v>1.325277872897482</v>
+        <v>1.360153606394784</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03156599601279991</v>
+        <v>0.03105686704485152</v>
       </c>
       <c r="W63">
-        <v>0.2283567381401818</v>
+        <v>0.228476790750824</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3507332890311102</v>
+        <v>0.3450763004983503</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1945795477708359</v>
+        <v>0.1964795477708359</v>
       </c>
       <c r="C64">
-        <v>-13.70688058835258</v>
+        <v>-15.36808303570263</v>
       </c>
       <c r="D64">
-        <v>47.04511941164742</v>
+        <v>46.57991696429737</v>
       </c>
       <c r="E64">
-        <v>36.052</v>
+        <v>37.248</v>
       </c>
       <c r="F64">
-        <v>74.152</v>
+        <v>75.348</v>
       </c>
       <c r="G64">
         <v>13.4</v>
@@ -6535,37 +6535,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M64">
-        <v>17.4850416</v>
+        <v>17.7670584</v>
       </c>
       <c r="N64">
-        <v>-11.45136813061225</v>
+        <v>-11.73338493061224</v>
       </c>
       <c r="O64">
-        <v>-1.030623131755102</v>
+        <v>-1.056004643755102</v>
       </c>
       <c r="P64">
-        <v>-10.42074499885715</v>
+        <v>-10.67738028685714</v>
       </c>
       <c r="Q64">
-        <v>-6.770744998857145</v>
+        <v>-7.027380286857142</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1392735197508554</v>
+        <v>0.1417998310954731</v>
       </c>
       <c r="T64">
-        <v>1.360153606394784</v>
+        <v>1.396914514675724</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03105686704485152</v>
+        <v>0.03056390090128245</v>
       </c>
       <c r="W64">
-        <v>0.228476790750824</v>
+        <v>0.2285930321674776</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3450763004983503</v>
+        <v>0.3395988989031384</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1964795477708359</v>
+        <v>0.1983795477708359</v>
       </c>
       <c r="C65">
-        <v>-15.36808303570263</v>
+        <v>-17.02017532304735</v>
       </c>
       <c r="D65">
-        <v>46.57991696429737</v>
+        <v>46.12382467695265</v>
       </c>
       <c r="E65">
-        <v>37.248</v>
+        <v>38.444</v>
       </c>
       <c r="F65">
-        <v>75.348</v>
+        <v>76.544</v>
       </c>
       <c r="G65">
         <v>13.4</v>
@@ -6617,37 +6617,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M65">
-        <v>17.7670584</v>
+        <v>18.0490752</v>
       </c>
       <c r="N65">
-        <v>-11.73338493061224</v>
+        <v>-12.01540173061225</v>
       </c>
       <c r="O65">
-        <v>-1.056004643755102</v>
+        <v>-1.081386155755102</v>
       </c>
       <c r="P65">
-        <v>-10.67738028685714</v>
+        <v>-10.93401557485714</v>
       </c>
       <c r="Q65">
-        <v>-7.027380286857142</v>
+        <v>-7.284015574857143</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1417998310954731</v>
+        <v>0.1444664930703473</v>
       </c>
       <c r="T65">
-        <v>1.396914514675724</v>
+        <v>1.435717695638939</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03056390090128245</v>
+        <v>0.03008633994969992</v>
       </c>
       <c r="W65">
-        <v>0.2285930321674776</v>
+        <v>0.2287056410398608</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3395988989031384</v>
+        <v>0.3342926661077769</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1983795477708359</v>
+        <v>0.200279547770836</v>
       </c>
       <c r="C66">
-        <v>-17.02017532304735</v>
+        <v>-18.66342246481593</v>
       </c>
       <c r="D66">
-        <v>46.12382467695265</v>
+        <v>45.67657753518407</v>
       </c>
       <c r="E66">
-        <v>38.444</v>
+        <v>39.63999999999999</v>
       </c>
       <c r="F66">
-        <v>76.544</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="G66">
         <v>13.4</v>
@@ -6699,37 +6699,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M66">
-        <v>18.0490752</v>
+        <v>18.331092</v>
       </c>
       <c r="N66">
-        <v>-12.01540173061225</v>
+        <v>-12.29741853061224</v>
       </c>
       <c r="O66">
-        <v>-1.081386155755102</v>
+        <v>-1.106767667755102</v>
       </c>
       <c r="P66">
-        <v>-10.93401557485714</v>
+        <v>-11.19065086285714</v>
       </c>
       <c r="Q66">
-        <v>-7.284015574857143</v>
+        <v>-7.54065086285714</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1444664930703473</v>
+        <v>0.1472855357295001</v>
       </c>
       <c r="T66">
-        <v>1.435717695638939</v>
+        <v>1.476738201228623</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03008633994969992</v>
+        <v>0.029623473181243</v>
       </c>
       <c r="W66">
-        <v>0.2287056410398608</v>
+        <v>0.2288147850238629</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3342926661077769</v>
+        <v>0.3291497020138111</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.200279547770836</v>
+        <v>0.2021795477708359</v>
       </c>
       <c r="C67">
-        <v>-18.66342246481593</v>
+        <v>-20.29807929513115</v>
       </c>
       <c r="D67">
-        <v>45.67657753518407</v>
+        <v>45.23792070486886</v>
       </c>
       <c r="E67">
-        <v>39.63999999999999</v>
+        <v>40.83600000000001</v>
       </c>
       <c r="F67">
-        <v>77.73999999999999</v>
+        <v>78.93600000000001</v>
       </c>
       <c r="G67">
         <v>13.4</v>
@@ -6781,37 +6781,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M67">
-        <v>18.331092</v>
+        <v>18.6131088</v>
       </c>
       <c r="N67">
-        <v>-12.29741853061224</v>
+        <v>-12.57943533061225</v>
       </c>
       <c r="O67">
-        <v>-1.106767667755102</v>
+        <v>-1.132149179755102</v>
       </c>
       <c r="P67">
-        <v>-11.19065086285714</v>
+        <v>-11.44728615085715</v>
       </c>
       <c r="Q67">
-        <v>-7.54065086285714</v>
+        <v>-7.797286150857145</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1472855357295001</v>
+        <v>0.1502704044274266</v>
       </c>
       <c r="T67">
-        <v>1.476738201228623</v>
+        <v>1.520171677735347</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.029623473181243</v>
+        <v>0.02917463267849688</v>
       </c>
       <c r="W67">
-        <v>0.2288147850238629</v>
+        <v>0.2289206216144105</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3291497020138111</v>
+        <v>0.324162585316632</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2021795477708359</v>
+        <v>0.2040795477708359</v>
       </c>
       <c r="C68">
-        <v>-20.29807929513115</v>
+        <v>-21.92439095199425</v>
       </c>
       <c r="D68">
-        <v>45.23792070486886</v>
+        <v>44.80760904800576</v>
       </c>
       <c r="E68">
-        <v>40.83600000000001</v>
+        <v>42.032</v>
       </c>
       <c r="F68">
-        <v>78.93600000000001</v>
+        <v>80.13200000000001</v>
       </c>
       <c r="G68">
         <v>13.4</v>
@@ -6863,37 +6863,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M68">
-        <v>18.6131088</v>
+        <v>18.8951256</v>
       </c>
       <c r="N68">
-        <v>-12.57943533061225</v>
+        <v>-12.86145213061225</v>
       </c>
       <c r="O68">
-        <v>-1.132149179755102</v>
+        <v>-1.157530691755102</v>
       </c>
       <c r="P68">
-        <v>-11.44728615085715</v>
+        <v>-11.70392143885715</v>
       </c>
       <c r="Q68">
-        <v>-7.797286150857145</v>
+        <v>-8.053921438857145</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1502704044274266</v>
+        <v>0.1534361742585607</v>
       </c>
       <c r="T68">
-        <v>1.520171677735347</v>
+        <v>1.56623748615157</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02917463267849688</v>
+        <v>0.02873919039971334</v>
       </c>
       <c r="W68">
-        <v>0.2289206216144105</v>
+        <v>0.2290232989037476</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.324162585316632</v>
+        <v>0.3193243377745928</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2040795477708359</v>
+        <v>0.205979547770836</v>
       </c>
       <c r="C69">
-        <v>-21.92439095199425</v>
+        <v>-23.54259333409649</v>
       </c>
       <c r="D69">
-        <v>44.80760904800576</v>
+        <v>44.38540666590351</v>
       </c>
       <c r="E69">
-        <v>42.032</v>
+        <v>43.228</v>
       </c>
       <c r="F69">
-        <v>80.13200000000001</v>
+        <v>81.328</v>
       </c>
       <c r="G69">
         <v>13.4</v>
@@ -6945,37 +6945,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M69">
-        <v>18.8951256</v>
+        <v>19.1771424</v>
       </c>
       <c r="N69">
-        <v>-12.86145213061225</v>
+        <v>-13.14346893061225</v>
       </c>
       <c r="O69">
-        <v>-1.157530691755102</v>
+        <v>-1.182912203755102</v>
       </c>
       <c r="P69">
-        <v>-11.70392143885715</v>
+        <v>-11.96055672685714</v>
       </c>
       <c r="Q69">
-        <v>-8.053921438857145</v>
+        <v>-8.310556726857143</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1534361742585607</v>
+        <v>0.1567998047041408</v>
       </c>
       <c r="T69">
-        <v>1.56623748615157</v>
+        <v>1.615182407593807</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02873919039971334</v>
+        <v>0.02831655524677639</v>
       </c>
       <c r="W69">
-        <v>0.2290232989037476</v>
+        <v>0.2291229562728102</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3193243377745928</v>
+        <v>0.3146283916308488</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.205979547770836</v>
+        <v>0.2078795477708359</v>
       </c>
       <c r="C70">
-        <v>-23.54259333409649</v>
+        <v>-25.15291353204554</v>
       </c>
       <c r="D70">
-        <v>44.38540666590351</v>
+        <v>43.97108646795446</v>
       </c>
       <c r="E70">
-        <v>43.228</v>
+        <v>44.424</v>
       </c>
       <c r="F70">
-        <v>81.328</v>
+        <v>82.524</v>
       </c>
       <c r="G70">
         <v>13.4</v>
@@ -7027,37 +7027,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M70">
-        <v>19.1771424</v>
+        <v>19.4591592</v>
       </c>
       <c r="N70">
-        <v>-13.14346893061225</v>
+        <v>-13.42548573061225</v>
       </c>
       <c r="O70">
-        <v>-1.182912203755102</v>
+        <v>-1.208293715755102</v>
       </c>
       <c r="P70">
-        <v>-11.96055672685714</v>
+        <v>-12.21719201485714</v>
       </c>
       <c r="Q70">
-        <v>-8.310556726857143</v>
+        <v>-8.567192014857143</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1567998047041408</v>
+        <v>0.1603804435655646</v>
       </c>
       <c r="T70">
-        <v>1.615182407593807</v>
+        <v>1.667285065903284</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02831655524677639</v>
+        <v>0.02790617038812745</v>
       </c>
       <c r="W70">
-        <v>0.2291229562728102</v>
+        <v>0.2292197250224796</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3146283916308488</v>
+        <v>0.3100685598680828</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2078795477708359</v>
+        <v>0.2097795477708359</v>
       </c>
       <c r="C71">
-        <v>-25.15291353204554</v>
+        <v>-26.75557023566348</v>
       </c>
       <c r="D71">
-        <v>43.97108646795446</v>
+        <v>43.56442976433652</v>
       </c>
       <c r="E71">
-        <v>44.424</v>
+        <v>45.62</v>
       </c>
       <c r="F71">
-        <v>82.524</v>
+        <v>83.72</v>
       </c>
       <c r="G71">
         <v>13.4</v>
@@ -7109,37 +7109,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M71">
-        <v>19.4591592</v>
+        <v>19.741176</v>
       </c>
       <c r="N71">
-        <v>-13.42548573061225</v>
+        <v>-13.70750253061224</v>
       </c>
       <c r="O71">
-        <v>-1.208293715755102</v>
+        <v>-1.233675227755102</v>
       </c>
       <c r="P71">
-        <v>-12.21719201485714</v>
+        <v>-12.47382730285714</v>
       </c>
       <c r="Q71">
-        <v>-8.567192014857143</v>
+        <v>-8.823827302857142</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1603804435655646</v>
+        <v>0.1641997916844168</v>
       </c>
       <c r="T71">
-        <v>1.667285065903284</v>
+        <v>1.722861234766727</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02790617038812745</v>
+        <v>0.02750751081115421</v>
       </c>
       <c r="W71">
-        <v>0.2292197250224796</v>
+        <v>0.2293137289507299</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3100685598680828</v>
+        <v>0.3056390090128246</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2097795477708359</v>
+        <v>0.2116795477708359</v>
       </c>
       <c r="C72">
-        <v>-26.75557023566348</v>
+        <v>-28.35077411889089</v>
       </c>
       <c r="D72">
-        <v>43.56442976433652</v>
+        <v>43.16522588110912</v>
       </c>
       <c r="E72">
-        <v>45.62</v>
+        <v>46.81600000000001</v>
       </c>
       <c r="F72">
-        <v>83.72</v>
+        <v>84.91600000000001</v>
       </c>
       <c r="G72">
         <v>13.4</v>
@@ -7191,37 +7191,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M72">
-        <v>19.741176</v>
+        <v>20.0231928</v>
       </c>
       <c r="N72">
-        <v>-13.70750253061224</v>
+        <v>-13.98951933061225</v>
       </c>
       <c r="O72">
-        <v>-1.233675227755102</v>
+        <v>-1.259056739755102</v>
       </c>
       <c r="P72">
-        <v>-12.47382730285714</v>
+        <v>-12.73046259085715</v>
       </c>
       <c r="Q72">
-        <v>-8.823827302857142</v>
+        <v>-9.080462590857145</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1641997916844168</v>
+        <v>0.1682825431218105</v>
       </c>
       <c r="T72">
-        <v>1.722861234766727</v>
+        <v>1.782270242862132</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02750751081115421</v>
+        <v>0.02712008108141964</v>
       </c>
       <c r="W72">
-        <v>0.2293137289507299</v>
+        <v>0.2294050848810013</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3056390090128246</v>
+        <v>0.301334234237996</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2116795477708359</v>
+        <v>0.2135795477708359</v>
       </c>
       <c r="C73">
-        <v>-28.35077411889088</v>
+        <v>-29.93872820372074</v>
       </c>
       <c r="D73">
-        <v>43.16522588110912</v>
+        <v>42.77327179627925</v>
       </c>
       <c r="E73">
-        <v>46.816</v>
+        <v>48.01199999999999</v>
       </c>
       <c r="F73">
-        <v>84.916</v>
+        <v>86.11199999999999</v>
       </c>
       <c r="G73">
         <v>13.4</v>
@@ -7273,37 +7273,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M73">
-        <v>20.0231928</v>
+        <v>20.3052096</v>
       </c>
       <c r="N73">
-        <v>-13.98951933061224</v>
+        <v>-14.27153613061225</v>
       </c>
       <c r="O73">
-        <v>-1.259056739755102</v>
+        <v>-1.284438251755102</v>
       </c>
       <c r="P73">
-        <v>-12.73046259085714</v>
+        <v>-12.98709787885714</v>
       </c>
       <c r="Q73">
-        <v>-9.080462590857142</v>
+        <v>-9.337097878857143</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1682825431218105</v>
+        <v>0.1726569196618751</v>
       </c>
       <c r="T73">
-        <v>1.782270242862131</v>
+        <v>1.845922751535778</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02712008108141964</v>
+        <v>0.02674341328862214</v>
       </c>
       <c r="W73">
-        <v>0.2294050848810013</v>
+        <v>0.2294939031465429</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.301334234237996</v>
+        <v>0.297149036540246</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2135795477708359</v>
+        <v>0.2154795477708359</v>
       </c>
       <c r="C74">
-        <v>-29.93872820372074</v>
+        <v>-31.51962820448297</v>
       </c>
       <c r="D74">
-        <v>42.77327179627925</v>
+        <v>42.38837179551702</v>
       </c>
       <c r="E74">
-        <v>48.01199999999999</v>
+        <v>49.20799999999999</v>
       </c>
       <c r="F74">
-        <v>86.11199999999999</v>
+        <v>87.30799999999999</v>
       </c>
       <c r="G74">
         <v>13.4</v>
@@ -7355,37 +7355,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M74">
-        <v>20.3052096</v>
+        <v>20.5872264</v>
       </c>
       <c r="N74">
-        <v>-14.27153613061225</v>
+        <v>-14.55355293061224</v>
       </c>
       <c r="O74">
-        <v>-1.284438251755102</v>
+        <v>-1.309819763755102</v>
       </c>
       <c r="P74">
-        <v>-12.98709787885714</v>
+        <v>-13.24373316685714</v>
       </c>
       <c r="Q74">
-        <v>-9.337097878857143</v>
+        <v>-9.59373316685714</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1726569196618751</v>
+        <v>0.1773553240937964</v>
       </c>
       <c r="T74">
-        <v>1.845922751535778</v>
+        <v>1.914290260851918</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02674341328862214</v>
+        <v>0.02637706516138075</v>
       </c>
       <c r="W74">
-        <v>0.2294939031465429</v>
+        <v>0.2295802880349464</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.297149036540246</v>
+        <v>0.2930785017931195</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2154795477708359</v>
+        <v>0.2173795477708359</v>
       </c>
       <c r="C75">
-        <v>-31.51962820448297</v>
+        <v>-33.09366285370604</v>
       </c>
       <c r="D75">
-        <v>42.38837179551702</v>
+        <v>42.01033714629396</v>
       </c>
       <c r="E75">
-        <v>49.20799999999999</v>
+        <v>50.40399999999999</v>
       </c>
       <c r="F75">
-        <v>87.30799999999999</v>
+        <v>88.50399999999999</v>
       </c>
       <c r="G75">
         <v>13.4</v>
@@ -7437,37 +7437,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M75">
-        <v>20.5872264</v>
+        <v>20.8692432</v>
       </c>
       <c r="N75">
-        <v>-14.55355293061224</v>
+        <v>-14.83556973061224</v>
       </c>
       <c r="O75">
-        <v>-1.309819763755102</v>
+        <v>-1.335201275755102</v>
       </c>
       <c r="P75">
-        <v>-13.24373316685714</v>
+        <v>-13.50036845485714</v>
       </c>
       <c r="Q75">
-        <v>-9.59373316685714</v>
+        <v>-9.850368454857142</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1773553240937964</v>
+        <v>0.1824151442512501</v>
       </c>
       <c r="T75">
-        <v>1.914290260851918</v>
+        <v>1.987916809346223</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02637706516138075</v>
+        <v>0.02602061833487561</v>
       </c>
       <c r="W75">
-        <v>0.2295802880349464</v>
+        <v>0.2296643381966363</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2930785017931195</v>
+        <v>0.2891179814986178</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2173795477708359</v>
+        <v>0.2192795477708359</v>
       </c>
       <c r="C76">
-        <v>-33.09366285370604</v>
+        <v>-34.6610142106961</v>
       </c>
       <c r="D76">
-        <v>42.01033714629396</v>
+        <v>41.6389857893039</v>
       </c>
       <c r="E76">
-        <v>50.40399999999999</v>
+        <v>51.59999999999999</v>
       </c>
       <c r="F76">
-        <v>88.50399999999999</v>
+        <v>89.69999999999999</v>
       </c>
       <c r="G76">
         <v>13.4</v>
@@ -7519,37 +7519,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M76">
-        <v>20.8692432</v>
+        <v>21.15126</v>
       </c>
       <c r="N76">
-        <v>-14.83556973061224</v>
+        <v>-15.11758653061224</v>
       </c>
       <c r="O76">
-        <v>-1.335201275755102</v>
+        <v>-1.360582787755102</v>
       </c>
       <c r="P76">
-        <v>-13.50036845485714</v>
+        <v>-13.75700374285714</v>
       </c>
       <c r="Q76">
-        <v>-9.850368454857142</v>
+        <v>-10.10700374285714</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1824151442512501</v>
+        <v>0.1878797500213002</v>
       </c>
       <c r="T76">
-        <v>1.987916809346223</v>
+        <v>2.067433481720072</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02602061833487561</v>
+        <v>0.02567367675707726</v>
       </c>
       <c r="W76">
-        <v>0.2296643381966363</v>
+        <v>0.2297461470206812</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2891179814986178</v>
+        <v>0.2852630750786362</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2192795477708359</v>
+        <v>0.2211795477708359</v>
       </c>
       <c r="C77">
-        <v>-34.6610142106961</v>
+        <v>-36.22185795389311</v>
       </c>
       <c r="D77">
-        <v>41.6389857893039</v>
+        <v>41.2741420461069</v>
       </c>
       <c r="E77">
-        <v>51.59999999999999</v>
+        <v>52.796</v>
       </c>
       <c r="F77">
-        <v>89.69999999999999</v>
+        <v>90.896</v>
       </c>
       <c r="G77">
         <v>13.4</v>
@@ -7601,37 +7601,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M77">
-        <v>21.15126</v>
+        <v>21.4332768</v>
       </c>
       <c r="N77">
-        <v>-15.11758653061224</v>
+        <v>-15.39960333061225</v>
       </c>
       <c r="O77">
-        <v>-1.360582787755102</v>
+        <v>-1.385964299755102</v>
       </c>
       <c r="P77">
-        <v>-13.75700374285714</v>
+        <v>-14.01363903085714</v>
       </c>
       <c r="Q77">
-        <v>-10.10700374285714</v>
+        <v>-10.36363903085714</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1878797500213002</v>
+        <v>0.193799739605521</v>
       </c>
       <c r="T77">
-        <v>2.067433481720072</v>
+        <v>2.153576543458408</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02567367675707726</v>
+        <v>0.02533586522079993</v>
       </c>
       <c r="W77">
-        <v>0.2297461470206812</v>
+        <v>0.2298258029809354</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2852630750786362</v>
+        <v>0.2815096135644436</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2211795477708359</v>
+        <v>0.2230795477708359</v>
       </c>
       <c r="C78">
-        <v>-36.22185795389311</v>
+        <v>-37.77636365799074</v>
       </c>
       <c r="D78">
-        <v>41.2741420461069</v>
+        <v>40.91563634200926</v>
       </c>
       <c r="E78">
-        <v>52.796</v>
+        <v>53.992</v>
       </c>
       <c r="F78">
-        <v>90.896</v>
+        <v>92.092</v>
       </c>
       <c r="G78">
         <v>13.4</v>
@@ -7683,37 +7683,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M78">
-        <v>21.4332768</v>
+        <v>21.7152936</v>
       </c>
       <c r="N78">
-        <v>-15.39960333061225</v>
+        <v>-15.68162013061224</v>
       </c>
       <c r="O78">
-        <v>-1.385964299755102</v>
+        <v>-1.411345811755102</v>
       </c>
       <c r="P78">
-        <v>-14.01363903085714</v>
+        <v>-14.27027431885714</v>
       </c>
       <c r="Q78">
-        <v>-10.36363903085714</v>
+        <v>-10.62027431885714</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.193799739605521</v>
+        <v>0.2002345108927175</v>
       </c>
       <c r="T78">
-        <v>2.153576543458408</v>
+        <v>2.24721030621747</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02533586522079993</v>
+        <v>0.02500682801014019</v>
       </c>
       <c r="W78">
-        <v>0.2298258029809354</v>
+        <v>0.229903389955209</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2815096135644436</v>
+        <v>0.2778536445571133</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2230795477708359</v>
+        <v>0.224979547770836</v>
       </c>
       <c r="C79">
-        <v>-37.77636365799074</v>
+        <v>-39.32469505673834</v>
       </c>
       <c r="D79">
-        <v>40.91563634200926</v>
+        <v>40.56330494326166</v>
       </c>
       <c r="E79">
-        <v>53.992</v>
+        <v>55.188</v>
       </c>
       <c r="F79">
-        <v>92.092</v>
+        <v>93.288</v>
       </c>
       <c r="G79">
         <v>13.4</v>
@@ -7765,37 +7765,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M79">
-        <v>21.7152936</v>
+        <v>21.9973104</v>
       </c>
       <c r="N79">
-        <v>-15.68162013061224</v>
+        <v>-15.96363693061224</v>
       </c>
       <c r="O79">
-        <v>-1.411345811755102</v>
+        <v>-1.436727323755102</v>
       </c>
       <c r="P79">
-        <v>-14.27027431885714</v>
+        <v>-14.52690960685714</v>
       </c>
       <c r="Q79">
-        <v>-10.62027431885714</v>
+        <v>-10.87690960685714</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2002345108927175</v>
+        <v>0.2072542613878411</v>
       </c>
       <c r="T79">
-        <v>2.24721030621747</v>
+        <v>2.349356229227355</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02500682801014019</v>
+        <v>0.02468622765103583</v>
       </c>
       <c r="W79">
-        <v>0.229903389955209</v>
+        <v>0.2299789875198858</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2778536445571133</v>
+        <v>0.2742914183448425</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.224979547770836</v>
+        <v>0.2268795477708359</v>
       </c>
       <c r="C80">
-        <v>-39.32469505673834</v>
+        <v>-40.86701029228042</v>
       </c>
       <c r="D80">
-        <v>40.56330494326166</v>
+        <v>40.21698970771958</v>
       </c>
       <c r="E80">
-        <v>55.188</v>
+        <v>56.38399999999999</v>
       </c>
       <c r="F80">
-        <v>93.288</v>
+        <v>94.48399999999999</v>
       </c>
       <c r="G80">
         <v>13.4</v>
@@ -7847,37 +7847,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M80">
-        <v>21.9973104</v>
+        <v>22.2793272</v>
       </c>
       <c r="N80">
-        <v>-15.96363693061224</v>
+        <v>-16.24565373061225</v>
       </c>
       <c r="O80">
-        <v>-1.436727323755102</v>
+        <v>-1.462108835755102</v>
       </c>
       <c r="P80">
-        <v>-14.52690960685714</v>
+        <v>-14.78354489485714</v>
       </c>
       <c r="Q80">
-        <v>-10.87690960685714</v>
+        <v>-11.13354489485714</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2072542613878411</v>
+        <v>0.2149425595491669</v>
       </c>
       <c r="T80">
-        <v>2.349356229227355</v>
+        <v>2.461230335381038</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02468622765103583</v>
+        <v>0.02437374375671892</v>
       </c>
       <c r="W80">
-        <v>0.2299789875198858</v>
+        <v>0.2300526712221657</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2742914183448425</v>
+        <v>0.2708193750746546</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2268795477708359</v>
+        <v>0.228779547770836</v>
       </c>
       <c r="C81">
-        <v>-40.86701029228042</v>
+        <v>-42.40346215183204</v>
       </c>
       <c r="D81">
-        <v>40.21698970771958</v>
+        <v>39.87653784816796</v>
       </c>
       <c r="E81">
-        <v>56.38399999999999</v>
+        <v>57.58000000000001</v>
       </c>
       <c r="F81">
-        <v>94.48399999999999</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="G81">
         <v>13.4</v>
@@ -7929,37 +7929,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M81">
-        <v>22.2793272</v>
+        <v>22.561344</v>
       </c>
       <c r="N81">
-        <v>-16.24565373061225</v>
+        <v>-16.52767053061225</v>
       </c>
       <c r="O81">
-        <v>-1.462108835755102</v>
+        <v>-1.487490347755102</v>
       </c>
       <c r="P81">
-        <v>-14.78354489485714</v>
+        <v>-15.04018018285715</v>
       </c>
       <c r="Q81">
-        <v>-11.13354489485714</v>
+        <v>-11.39018018285715</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2149425595491669</v>
+        <v>0.2233996875266252</v>
       </c>
       <c r="T81">
-        <v>2.461230335381038</v>
+        <v>2.58429185215009</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02437374375671892</v>
+        <v>0.02406907195975993</v>
       </c>
       <c r="W81">
-        <v>0.2300526712221657</v>
+        <v>0.2301245128318886</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2708193750746546</v>
+        <v>0.2674341328862214</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.228779547770836</v>
+        <v>0.2306795477708359</v>
       </c>
       <c r="C82">
-        <v>-42.40346215183204</v>
+        <v>-43.93419829243327</v>
       </c>
       <c r="D82">
-        <v>39.87653784816796</v>
+        <v>39.54180170756674</v>
       </c>
       <c r="E82">
-        <v>57.58000000000001</v>
+        <v>58.776</v>
       </c>
       <c r="F82">
-        <v>95.68000000000001</v>
+        <v>96.876</v>
       </c>
       <c r="G82">
         <v>13.4</v>
@@ -8011,37 +8011,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M82">
-        <v>22.561344</v>
+        <v>22.8433608</v>
       </c>
       <c r="N82">
-        <v>-16.52767053061225</v>
+        <v>-16.80968733061225</v>
       </c>
       <c r="O82">
-        <v>-1.487490347755102</v>
+        <v>-1.512871859755102</v>
       </c>
       <c r="P82">
-        <v>-15.04018018285715</v>
+        <v>-15.29681547085715</v>
       </c>
       <c r="Q82">
-        <v>-11.39018018285715</v>
+        <v>-11.64681547085715</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2233996875266252</v>
+        <v>0.2327470395017108</v>
       </c>
       <c r="T82">
-        <v>2.58429185215009</v>
+        <v>2.720307212789569</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02406907195975993</v>
+        <v>0.02377192292321968</v>
       </c>
       <c r="W82">
-        <v>0.2301245128318886</v>
+        <v>0.2301945805747048</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2674341328862214</v>
+        <v>0.2641324769246631</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2306795477708359</v>
+        <v>0.2325795477708359</v>
       </c>
       <c r="C83">
-        <v>-43.93419829243327</v>
+        <v>-45.45936145447849</v>
       </c>
       <c r="D83">
-        <v>39.54180170756674</v>
+        <v>39.21263854552151</v>
       </c>
       <c r="E83">
-        <v>58.776</v>
+        <v>59.972</v>
       </c>
       <c r="F83">
-        <v>96.876</v>
+        <v>98.072</v>
       </c>
       <c r="G83">
         <v>13.4</v>
@@ -8093,37 +8093,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M83">
-        <v>22.8433608</v>
+        <v>23.1253776</v>
       </c>
       <c r="N83">
-        <v>-16.80968733061225</v>
+        <v>-17.09170413061224</v>
       </c>
       <c r="O83">
-        <v>-1.512871859755102</v>
+        <v>-1.538253371755102</v>
       </c>
       <c r="P83">
-        <v>-15.29681547085715</v>
+        <v>-15.55345075885714</v>
       </c>
       <c r="Q83">
-        <v>-11.64681547085715</v>
+        <v>-11.90345075885714</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2327470395017108</v>
+        <v>0.2431329861406947</v>
       </c>
       <c r="T83">
-        <v>2.720307212789569</v>
+        <v>2.871435391277879</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02377192292321968</v>
+        <v>0.02348202142415603</v>
       </c>
       <c r="W83">
-        <v>0.2301945805747048</v>
+        <v>0.230262939348184</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2641324769246631</v>
+        <v>0.2609113491572893</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2325795477708359</v>
+        <v>0.2344795477708359</v>
       </c>
       <c r="C84">
-        <v>-45.45936145447849</v>
+        <v>-46.97908966466829</v>
       </c>
       <c r="D84">
-        <v>39.21263854552151</v>
+        <v>38.88891033533171</v>
       </c>
       <c r="E84">
-        <v>59.972</v>
+        <v>61.168</v>
       </c>
       <c r="F84">
-        <v>98.072</v>
+        <v>99.268</v>
       </c>
       <c r="G84">
         <v>13.4</v>
@@ -8175,37 +8175,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M84">
-        <v>23.1253776</v>
+        <v>23.4073944</v>
       </c>
       <c r="N84">
-        <v>-17.09170413061224</v>
+        <v>-17.37372093061224</v>
       </c>
       <c r="O84">
-        <v>-1.538253371755102</v>
+        <v>-1.563634883755102</v>
       </c>
       <c r="P84">
-        <v>-15.55345075885714</v>
+        <v>-15.81008604685714</v>
       </c>
       <c r="Q84">
-        <v>-11.90345075885714</v>
+        <v>-12.16008604685714</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2431329861406947</v>
+        <v>0.2547408088548532</v>
       </c>
       <c r="T84">
-        <v>2.871435391277879</v>
+        <v>3.040343355470695</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02348202142415603</v>
+        <v>0.02319910550338307</v>
       </c>
       <c r="W84">
-        <v>0.230262939348184</v>
+        <v>0.2303296509223023</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2609113491572893</v>
+        <v>0.2577678389264786</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2344795477708359</v>
+        <v>0.2363795477708359</v>
       </c>
       <c r="C85">
-        <v>-46.97908966466829</v>
+        <v>-48.4935164289908</v>
       </c>
       <c r="D85">
-        <v>38.88891033533171</v>
+        <v>38.5704835710092</v>
       </c>
       <c r="E85">
-        <v>61.168</v>
+        <v>62.364</v>
       </c>
       <c r="F85">
-        <v>99.268</v>
+        <v>100.464</v>
       </c>
       <c r="G85">
         <v>13.4</v>
@@ -8257,37 +8257,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M85">
-        <v>23.4073944</v>
+        <v>23.6894112</v>
       </c>
       <c r="N85">
-        <v>-17.37372093061224</v>
+        <v>-17.65573773061224</v>
       </c>
       <c r="O85">
-        <v>-1.563634883755102</v>
+        <v>-1.589016395755102</v>
       </c>
       <c r="P85">
-        <v>-15.81008604685714</v>
+        <v>-16.06672133485714</v>
       </c>
       <c r="Q85">
-        <v>-12.16008604685714</v>
+        <v>-12.41672133485714</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2547408088548532</v>
+        <v>0.2677996094082816</v>
       </c>
       <c r="T85">
-        <v>3.040343355470695</v>
+        <v>3.230364815187614</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02319910550338307</v>
+        <v>0.02292292567596184</v>
       </c>
       <c r="W85">
-        <v>0.2303296509223023</v>
+        <v>0.2303947741256082</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2577678389264786</v>
+        <v>0.2546991741773539</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2363795477708359</v>
+        <v>0.238279547770836</v>
       </c>
       <c r="C86">
-        <v>-48.49351642899079</v>
+        <v>-50.00277091629897</v>
       </c>
       <c r="D86">
-        <v>38.5704835710092</v>
+        <v>38.25722908370103</v>
       </c>
       <c r="E86">
-        <v>62.36399999999998</v>
+        <v>63.56</v>
       </c>
       <c r="F86">
-        <v>100.464</v>
+        <v>101.66</v>
       </c>
       <c r="G86">
         <v>13.4</v>
@@ -8339,37 +8339,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M86">
-        <v>23.6894112</v>
+        <v>23.971428</v>
       </c>
       <c r="N86">
-        <v>-17.65573773061224</v>
+        <v>-17.93775453061225</v>
       </c>
       <c r="O86">
-        <v>-1.589016395755102</v>
+        <v>-1.614397907755102</v>
       </c>
       <c r="P86">
-        <v>-16.06672133485714</v>
+        <v>-16.32335662285714</v>
       </c>
       <c r="Q86">
-        <v>-12.41672133485714</v>
+        <v>-12.67335662285714</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2677996094082814</v>
+        <v>0.2825995833688336</v>
       </c>
       <c r="T86">
-        <v>3.230364815187612</v>
+        <v>3.445722469533453</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02292292567596184</v>
+        <v>0.02265324419742111</v>
       </c>
       <c r="W86">
-        <v>0.2303947741256082</v>
+        <v>0.2304583650182481</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2546991741773538</v>
+        <v>0.251702713304679</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.238279547770836</v>
+        <v>0.2401795477708359</v>
       </c>
       <c r="C87">
-        <v>-50.00277091629897</v>
+        <v>-51.50697813301439</v>
       </c>
       <c r="D87">
-        <v>38.25722908370103</v>
+        <v>37.9490218669856</v>
       </c>
       <c r="E87">
-        <v>63.56</v>
+        <v>64.756</v>
       </c>
       <c r="F87">
-        <v>101.66</v>
+        <v>102.856</v>
       </c>
       <c r="G87">
         <v>13.4</v>
@@ -8421,37 +8421,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M87">
-        <v>23.971428</v>
+        <v>24.2534448</v>
       </c>
       <c r="N87">
-        <v>-17.93775453061225</v>
+        <v>-18.21977133061225</v>
       </c>
       <c r="O87">
-        <v>-1.614397907755102</v>
+        <v>-1.639779419755102</v>
       </c>
       <c r="P87">
-        <v>-16.32335662285714</v>
+        <v>-16.57999191085715</v>
       </c>
       <c r="Q87">
-        <v>-12.67335662285714</v>
+        <v>-12.92999191085715</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2825995833688336</v>
+        <v>0.2995138393237503</v>
       </c>
       <c r="T87">
-        <v>3.445722469533453</v>
+        <v>3.691845503071557</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02265324419742111</v>
+        <v>0.02238983438117203</v>
       </c>
       <c r="W87">
-        <v>0.2304583650182481</v>
+        <v>0.2305204770529196</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.251702713304679</v>
+        <v>0.2487759375685781</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2401795477708359</v>
+        <v>0.2420795477708359</v>
       </c>
       <c r="C88">
-        <v>-51.50697813301439</v>
+        <v>-53.00625908945389</v>
       </c>
       <c r="D88">
-        <v>37.9490218669856</v>
+        <v>37.6457409105461</v>
       </c>
       <c r="E88">
-        <v>64.756</v>
+        <v>65.952</v>
       </c>
       <c r="F88">
-        <v>102.856</v>
+        <v>104.052</v>
       </c>
       <c r="G88">
         <v>13.4</v>
@@ -8503,37 +8503,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M88">
-        <v>24.2534448</v>
+        <v>24.5354616</v>
       </c>
       <c r="N88">
-        <v>-18.21977133061225</v>
+        <v>-18.50178813061224</v>
       </c>
       <c r="O88">
-        <v>-1.639779419755102</v>
+        <v>-1.665160931755101</v>
       </c>
       <c r="P88">
-        <v>-16.57999191085715</v>
+        <v>-16.83662719885714</v>
       </c>
       <c r="Q88">
-        <v>-12.92999191085715</v>
+        <v>-13.18662719885714</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2995138393237503</v>
+        <v>0.3190302885025003</v>
       </c>
       <c r="T88">
-        <v>3.691845503071557</v>
+        <v>3.975833618692446</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02238983438117203</v>
+        <v>0.02213247996299764</v>
       </c>
       <c r="W88">
-        <v>0.2305204770529196</v>
+        <v>0.2305811612247252</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2487759375685781</v>
+        <v>0.2459164440333071</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2420795477708359</v>
+        <v>0.2439795477708359</v>
       </c>
       <c r="C89">
-        <v>-53.00625908945389</v>
+        <v>-54.50073095824376</v>
       </c>
       <c r="D89">
-        <v>37.6457409105461</v>
+        <v>37.34726904175623</v>
       </c>
       <c r="E89">
-        <v>65.952</v>
+        <v>67.148</v>
       </c>
       <c r="F89">
-        <v>104.052</v>
+        <v>105.248</v>
       </c>
       <c r="G89">
         <v>13.4</v>
@@ -8585,37 +8585,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M89">
-        <v>24.5354616</v>
+        <v>24.8174784</v>
       </c>
       <c r="N89">
-        <v>-18.50178813061224</v>
+        <v>-18.78380493061224</v>
       </c>
       <c r="O89">
-        <v>-1.665160931755101</v>
+        <v>-1.690542443755102</v>
       </c>
       <c r="P89">
-        <v>-16.83662719885714</v>
+        <v>-17.09326248685714</v>
       </c>
       <c r="Q89">
-        <v>-13.18662719885714</v>
+        <v>-13.44326248685714</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3190302885025003</v>
+        <v>0.341799479211042</v>
       </c>
       <c r="T89">
-        <v>3.975833618692446</v>
+        <v>4.307153086916816</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02213247996299764</v>
+        <v>0.02188097450887267</v>
       </c>
       <c r="W89">
-        <v>0.2305811612247252</v>
+        <v>0.2306404662108078</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2459164440333071</v>
+        <v>0.2431219389874741</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2439795477708359</v>
+        <v>0.2458795477708359</v>
       </c>
       <c r="C90">
-        <v>-54.50073095824376</v>
+        <v>-55.99050722525759</v>
       </c>
       <c r="D90">
-        <v>37.34726904175623</v>
+        <v>37.05349277474242</v>
       </c>
       <c r="E90">
-        <v>67.148</v>
+        <v>68.34399999999999</v>
       </c>
       <c r="F90">
-        <v>105.248</v>
+        <v>106.444</v>
       </c>
       <c r="G90">
         <v>13.4</v>
@@ -8667,37 +8667,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M90">
-        <v>24.8174784</v>
+        <v>25.0994952</v>
       </c>
       <c r="N90">
-        <v>-18.78380493061224</v>
+        <v>-19.06582173061225</v>
       </c>
       <c r="O90">
-        <v>-1.690542443755102</v>
+        <v>-1.715923955755102</v>
       </c>
       <c r="P90">
-        <v>-17.09326248685714</v>
+        <v>-17.34989777485715</v>
       </c>
       <c r="Q90">
-        <v>-13.44326248685714</v>
+        <v>-13.69989777485715</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.341799479211042</v>
+        <v>0.3687085227756822</v>
       </c>
       <c r="T90">
-        <v>4.307153086916816</v>
+        <v>4.698712458454709</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02188097450887267</v>
+        <v>0.02163512086270555</v>
       </c>
       <c r="W90">
-        <v>0.2306404662108078</v>
+        <v>0.230698438500574</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2431219389874741</v>
+        <v>0.2403902318078395</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2458795477708359</v>
+        <v>0.2477795477708359</v>
       </c>
       <c r="C91">
-        <v>-55.99050722525759</v>
+        <v>-57.47569783348576</v>
       </c>
       <c r="D91">
-        <v>37.05349277474242</v>
+        <v>36.76430216651424</v>
       </c>
       <c r="E91">
-        <v>68.34399999999999</v>
+        <v>69.53999999999999</v>
       </c>
       <c r="F91">
-        <v>106.444</v>
+        <v>107.64</v>
       </c>
       <c r="G91">
         <v>13.4</v>
@@ -8749,37 +8749,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M91">
-        <v>25.0994952</v>
+        <v>25.381512</v>
       </c>
       <c r="N91">
-        <v>-19.06582173061225</v>
+        <v>-19.34783853061224</v>
       </c>
       <c r="O91">
-        <v>-1.715923955755102</v>
+        <v>-1.741305467755102</v>
       </c>
       <c r="P91">
-        <v>-17.34989777485715</v>
+        <v>-17.60653306285714</v>
       </c>
       <c r="Q91">
-        <v>-13.69989777485715</v>
+        <v>-13.95653306285714</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3687085227756822</v>
+        <v>0.4009993750532505</v>
       </c>
       <c r="T91">
-        <v>4.698712458454709</v>
+        <v>5.168583704300182</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02163512086270555</v>
+        <v>0.02139473063089772</v>
       </c>
       <c r="W91">
-        <v>0.230698438500574</v>
+        <v>0.2307551225172343</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2403902318078395</v>
+        <v>0.2377192292321969</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2477795477708359</v>
+        <v>0.249679547770836</v>
       </c>
       <c r="C92">
-        <v>-57.47569783348576</v>
+        <v>-58.95640932022018</v>
       </c>
       <c r="D92">
-        <v>36.76430216651424</v>
+        <v>36.47959067977982</v>
       </c>
       <c r="E92">
-        <v>69.53999999999999</v>
+        <v>70.73599999999999</v>
       </c>
       <c r="F92">
-        <v>107.64</v>
+        <v>108.836</v>
       </c>
       <c r="G92">
         <v>13.4</v>
@@ -8831,37 +8831,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M92">
-        <v>25.381512</v>
+        <v>25.6635288</v>
       </c>
       <c r="N92">
-        <v>-19.34783853061224</v>
+        <v>-19.62985533061224</v>
       </c>
       <c r="O92">
-        <v>-1.741305467755102</v>
+        <v>-1.766686979755102</v>
       </c>
       <c r="P92">
-        <v>-17.60653306285714</v>
+        <v>-17.86316835085714</v>
       </c>
       <c r="Q92">
-        <v>-13.95653306285714</v>
+        <v>-14.21316835085714</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4009993750532505</v>
+        <v>0.4404659722813894</v>
       </c>
       <c r="T92">
-        <v>5.168583704300182</v>
+        <v>5.742870782555757</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02139473063089772</v>
+        <v>0.02115962370088785</v>
       </c>
       <c r="W92">
-        <v>0.2307551225172343</v>
+        <v>0.2308105607313307</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2377192292321969</v>
+        <v>0.235106930009865</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.249679547770836</v>
+        <v>0.2515795477708359</v>
       </c>
       <c r="C93">
-        <v>-58.95640932022018</v>
+        <v>-60.43274494791353</v>
       </c>
       <c r="D93">
-        <v>36.47959067977982</v>
+        <v>36.19925505208647</v>
       </c>
       <c r="E93">
-        <v>70.73599999999999</v>
+        <v>71.93199999999999</v>
       </c>
       <c r="F93">
-        <v>108.836</v>
+        <v>110.032</v>
       </c>
       <c r="G93">
         <v>13.4</v>
@@ -8913,37 +8913,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M93">
-        <v>25.6635288</v>
+        <v>25.9455456</v>
       </c>
       <c r="N93">
-        <v>-19.62985533061224</v>
+        <v>-19.91187213061225</v>
       </c>
       <c r="O93">
-        <v>-1.766686979755102</v>
+        <v>-1.792068491755102</v>
       </c>
       <c r="P93">
-        <v>-17.86316835085714</v>
+        <v>-18.11980363885714</v>
       </c>
       <c r="Q93">
-        <v>-14.21316835085714</v>
+        <v>-14.46980363885714</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4404659722813894</v>
+        <v>0.4897992188165632</v>
       </c>
       <c r="T93">
-        <v>5.742870782555757</v>
+        <v>6.460729630375228</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02115962370088785</v>
+        <v>0.02092962779109559</v>
       </c>
       <c r="W93">
-        <v>0.2308105607313307</v>
+        <v>0.2308647937668596</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.235106930009865</v>
+        <v>0.2325514199010621</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2515795477708359</v>
+        <v>0.2534795477708359</v>
       </c>
       <c r="C94">
-        <v>-60.43274494791353</v>
+        <v>-61.90480482905088</v>
       </c>
       <c r="D94">
-        <v>36.19925505208647</v>
+        <v>35.92319517094911</v>
       </c>
       <c r="E94">
-        <v>71.93199999999999</v>
+        <v>73.12799999999999</v>
       </c>
       <c r="F94">
-        <v>110.032</v>
+        <v>111.228</v>
       </c>
       <c r="G94">
         <v>13.4</v>
@@ -8995,37 +8995,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M94">
-        <v>25.9455456</v>
+        <v>26.2275624</v>
       </c>
       <c r="N94">
-        <v>-19.91187213061225</v>
+        <v>-20.19388893061225</v>
       </c>
       <c r="O94">
-        <v>-1.792068491755102</v>
+        <v>-1.817450003755102</v>
       </c>
       <c r="P94">
-        <v>-18.11980363885714</v>
+        <v>-18.37643892685714</v>
       </c>
       <c r="Q94">
-        <v>-14.46980363885714</v>
+        <v>-14.72643892685714</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4897992188165632</v>
+        <v>0.5532276786475008</v>
       </c>
       <c r="T94">
-        <v>6.460729630375228</v>
+        <v>7.38369100614312</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02092962779109559</v>
+        <v>0.02070457802990102</v>
       </c>
       <c r="W94">
-        <v>0.2308647937668596</v>
+        <v>0.2309178605005494</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2325514199010621</v>
+        <v>0.2300508669989001</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2534795477708359</v>
+        <v>0.2553795477708359</v>
       </c>
       <c r="C95">
-        <v>-61.90480482905088</v>
+        <v>-63.37268604535076</v>
       </c>
       <c r="D95">
-        <v>35.92319517094911</v>
+        <v>35.65131395464925</v>
       </c>
       <c r="E95">
-        <v>73.12799999999999</v>
+        <v>74.32400000000001</v>
       </c>
       <c r="F95">
-        <v>111.228</v>
+        <v>112.424</v>
       </c>
       <c r="G95">
         <v>13.4</v>
@@ -9077,37 +9077,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M95">
-        <v>26.2275624</v>
+        <v>26.5095792</v>
       </c>
       <c r="N95">
-        <v>-20.19388893061225</v>
+        <v>-20.47590573061225</v>
       </c>
       <c r="O95">
-        <v>-1.817450003755102</v>
+        <v>-1.842831515755102</v>
       </c>
       <c r="P95">
-        <v>-18.37643892685714</v>
+        <v>-18.63307421485715</v>
       </c>
       <c r="Q95">
-        <v>-14.72643892685714</v>
+        <v>-14.98307421485715</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5532276786475008</v>
+        <v>0.6377989584220843</v>
       </c>
       <c r="T95">
-        <v>7.38369100614312</v>
+        <v>8.61430617383364</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02070457802990102</v>
+        <v>0.02048431656149781</v>
       </c>
       <c r="W95">
-        <v>0.2309178605005494</v>
+        <v>0.2309697981547988</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2300508669989001</v>
+        <v>0.2276035173499756</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2553795477708359</v>
+        <v>0.2572795477708359</v>
       </c>
       <c r="C96">
-        <v>-63.37268604535076</v>
+        <v>-64.836482761594</v>
       </c>
       <c r="D96">
-        <v>35.65131395464925</v>
+        <v>35.383517238406</v>
       </c>
       <c r="E96">
-        <v>74.32400000000001</v>
+        <v>75.52000000000001</v>
       </c>
       <c r="F96">
-        <v>112.424</v>
+        <v>113.62</v>
       </c>
       <c r="G96">
         <v>13.4</v>
@@ -9159,37 +9159,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M96">
-        <v>26.5095792</v>
+        <v>26.791596</v>
       </c>
       <c r="N96">
-        <v>-20.47590573061225</v>
+        <v>-20.75792253061225</v>
       </c>
       <c r="O96">
-        <v>-1.842831515755102</v>
+        <v>-1.868213027755102</v>
       </c>
       <c r="P96">
-        <v>-18.63307421485715</v>
+        <v>-18.88970950285714</v>
       </c>
       <c r="Q96">
-        <v>-14.98307421485715</v>
+        <v>-15.23970950285714</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6377989584220843</v>
+        <v>0.7561987501065016</v>
       </c>
       <c r="T96">
-        <v>8.61430617383364</v>
+        <v>10.33716740860037</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02048431656149781</v>
+        <v>0.02026869217663994</v>
       </c>
       <c r="W96">
-        <v>0.2309697981547988</v>
+        <v>0.2310206423847483</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2276035173499756</v>
+        <v>0.2252076908515549</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2572795477708359</v>
+        <v>0.259179547770836</v>
       </c>
       <c r="C97">
-        <v>-64.836482761594</v>
+        <v>-66.29628633436064</v>
       </c>
       <c r="D97">
-        <v>35.383517238406</v>
+        <v>35.11971366563936</v>
       </c>
       <c r="E97">
-        <v>75.52000000000001</v>
+        <v>76.71600000000001</v>
       </c>
       <c r="F97">
-        <v>113.62</v>
+        <v>114.816</v>
       </c>
       <c r="G97">
         <v>13.4</v>
@@ -9241,37 +9241,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M97">
-        <v>26.791596</v>
+        <v>27.0736128</v>
       </c>
       <c r="N97">
-        <v>-20.75792253061225</v>
+        <v>-21.03993933061225</v>
       </c>
       <c r="O97">
-        <v>-1.868213027755102</v>
+        <v>-1.893594539755102</v>
       </c>
       <c r="P97">
-        <v>-18.88970950285714</v>
+        <v>-19.14634479085715</v>
       </c>
       <c r="Q97">
-        <v>-15.23970950285714</v>
+        <v>-15.49634479085715</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7561987501065016</v>
+        <v>0.9337984376331275</v>
       </c>
       <c r="T97">
-        <v>10.33716740860037</v>
+        <v>12.92145926075047</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02026869217663994</v>
+        <v>0.02005755996646661</v>
       </c>
       <c r="W97">
-        <v>0.2310206423847483</v>
+        <v>0.2310704273599072</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2252076908515549</v>
+        <v>0.2228617774051844</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.259179547770836</v>
+        <v>0.2610795477708359</v>
       </c>
       <c r="C98">
-        <v>-66.29628633436063</v>
+        <v>-67.75218541593853</v>
       </c>
       <c r="D98">
-        <v>35.11971366563936</v>
+        <v>34.85981458406146</v>
       </c>
       <c r="E98">
-        <v>76.71599999999998</v>
+        <v>77.91199999999998</v>
       </c>
       <c r="F98">
-        <v>114.816</v>
+        <v>116.012</v>
       </c>
       <c r="G98">
         <v>13.4</v>
@@ -9323,37 +9323,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M98">
-        <v>27.0736128</v>
+        <v>27.3556296</v>
       </c>
       <c r="N98">
-        <v>-21.03993933061224</v>
+        <v>-21.32195613061224</v>
       </c>
       <c r="O98">
-        <v>-1.893594539755102</v>
+        <v>-1.918976051755102</v>
       </c>
       <c r="P98">
-        <v>-19.14634479085714</v>
+        <v>-19.40298007885714</v>
       </c>
       <c r="Q98">
-        <v>-15.49634479085714</v>
+        <v>-15.75298007885714</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9337984376331251</v>
+        <v>1.229797916844167</v>
       </c>
       <c r="T98">
-        <v>12.92145926075044</v>
+        <v>17.22861234766725</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02005755996646661</v>
+        <v>0.01985078099774015</v>
       </c>
       <c r="W98">
-        <v>0.2310704273599072</v>
+        <v>0.2311191858407329</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2228617774051846</v>
+        <v>0.2205642333082238</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2610795477708359</v>
+        <v>0.2629795477708359</v>
       </c>
       <c r="C99">
-        <v>-67.75218541593853</v>
+        <v>-69.2042660536523</v>
       </c>
       <c r="D99">
-        <v>34.85981458406146</v>
+        <v>34.6037339463477</v>
       </c>
       <c r="E99">
-        <v>77.91199999999998</v>
+        <v>79.108</v>
       </c>
       <c r="F99">
-        <v>116.012</v>
+        <v>117.208</v>
       </c>
       <c r="G99">
         <v>13.4</v>
@@ -9405,37 +9405,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M99">
-        <v>27.3556296</v>
+        <v>27.6376464</v>
       </c>
       <c r="N99">
-        <v>-21.32195613061224</v>
+        <v>-21.60397293061224</v>
       </c>
       <c r="O99">
-        <v>-1.918976051755102</v>
+        <v>-1.944357563755102</v>
       </c>
       <c r="P99">
-        <v>-19.40298007885714</v>
+        <v>-19.65961536685714</v>
       </c>
       <c r="Q99">
-        <v>-15.75298007885714</v>
+        <v>-16.00961536685714</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.229797916844167</v>
+        <v>1.82179687526625</v>
       </c>
       <c r="T99">
-        <v>17.22861234766725</v>
+        <v>25.84291852150088</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01985078099774015</v>
+        <v>0.01964822200796729</v>
       </c>
       <c r="W99">
-        <v>0.2311191858407329</v>
+        <v>0.2311669492505213</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2205642333082238</v>
+        <v>0.2183135778663033</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2629795477708359</v>
+        <v>0.2648795477708359</v>
       </c>
       <c r="C100">
-        <v>-69.2042660536523</v>
+        <v>-70.65261178484596</v>
       </c>
       <c r="D100">
-        <v>34.6037339463477</v>
+        <v>34.35138821515405</v>
       </c>
       <c r="E100">
-        <v>79.108</v>
+        <v>80.304</v>
       </c>
       <c r="F100">
-        <v>117.208</v>
+        <v>118.404</v>
       </c>
       <c r="G100">
         <v>13.4</v>
@@ -9487,37 +9487,37 @@
         <v>6.033673469387756</v>
       </c>
       <c r="M100">
-        <v>27.6376464</v>
+        <v>27.9196632</v>
       </c>
       <c r="N100">
-        <v>-21.60397293061224</v>
+        <v>-21.88598973061224</v>
       </c>
       <c r="O100">
-        <v>-1.944357563755102</v>
+        <v>-1.969739075755102</v>
       </c>
       <c r="P100">
-        <v>-19.65961536685714</v>
+        <v>-19.91625065485714</v>
       </c>
       <c r="Q100">
-        <v>-16.00961536685714</v>
+        <v>-16.26625065485715</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.82179687526625</v>
+        <v>3.5977937505325</v>
       </c>
       <c r="T100">
-        <v>25.84291852150088</v>
+        <v>51.68583704300175</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01964822200796729</v>
+        <v>0.01944975511899793</v>
       </c>
       <c r="W100">
-        <v>0.2311669492505213</v>
+        <v>0.2312137477429403</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2183135778663033</v>
+        <v>0.216108390211088</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2648795477708359</v>
-      </c>
-      <c r="C101">
-        <v>-70.65261178484596</v>
-      </c>
-      <c r="D101">
-        <v>34.35138821515405</v>
-      </c>
-      <c r="E101">
-        <v>80.304</v>
-      </c>
-      <c r="F101">
-        <v>118.404</v>
-      </c>
-      <c r="G101">
-        <v>13.4</v>
-      </c>
-      <c r="H101">
-        <v>81.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.683673469387756</v>
-      </c>
-      <c r="K101">
-        <v>3.65</v>
-      </c>
-      <c r="L101">
-        <v>6.033673469387756</v>
-      </c>
-      <c r="M101">
-        <v>27.9196632</v>
-      </c>
-      <c r="N101">
-        <v>-21.88598973061224</v>
-      </c>
-      <c r="O101">
-        <v>-1.969739075755102</v>
-      </c>
-      <c r="P101">
-        <v>-19.91625065485714</v>
-      </c>
-      <c r="Q101">
-        <v>-16.26625065485715</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.5977937505325</v>
-      </c>
-      <c r="T101">
-        <v>51.68583704300175</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01944975511899793</v>
-      </c>
-      <c r="W101">
-        <v>0.2312137477429403</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.216108390211088</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
